--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit1_1_DownSamplingL.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit1_1_DownSamplingL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A6247D-D824-4B3C-8244-EBE3A1397EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C739512-7C3D-42FC-BDEE-DCACEE8F77DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8075A957-5B64-468D-B2D4-F19799456396}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{8075A957-5B64-468D-B2D4-F19799456396}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="85">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -376,6 +376,10 @@
     <t>32*(24/4)*2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Requant_Sel[3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -608,7 +612,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -620,10 +627,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1089,6 +1093,9 @@
       <c r="M5" s="8" t="s">
         <v>73</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
@@ -1099,7 +1106,7 @@
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="23"/>
@@ -1134,7 +1141,7 @@
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
-      <c r="F8" s="29"/>
+      <c r="F8" s="24"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
@@ -1177,7 +1184,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="24"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
@@ -1201,7 +1208,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
-      <c r="F10" s="29"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
@@ -1232,7 +1239,7 @@
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
-      <c r="F11" s="29"/>
+      <c r="F11" s="24"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
@@ -1266,7 +1273,7 @@
       <c r="F12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="23"/>
@@ -1301,7 +1308,7 @@
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -1344,7 +1351,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
-      <c r="G14" s="29"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -1368,7 +1375,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
-      <c r="G15" s="29"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -1399,7 +1406,7 @@
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
-      <c r="G16" s="29"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -1426,14 +1433,14 @@
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="28" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="23"/>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="25" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="23"/>
@@ -1462,10 +1469,10 @@
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
       <c r="H18" s="23"/>
-      <c r="I18" s="28"/>
+      <c r="I18" s="25"/>
       <c r="J18" s="23"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
@@ -1505,10 +1512,10 @@
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="23"/>
-      <c r="I19" s="28"/>
+      <c r="I19" s="25"/>
       <c r="J19" s="23"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
@@ -1538,10 +1545,10 @@
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="23"/>
-      <c r="I20" s="28"/>
+      <c r="I20" s="25"/>
       <c r="J20" s="23"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
@@ -1568,10 +1575,10 @@
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="23"/>
-      <c r="I21" s="28"/>
+      <c r="I21" s="25"/>
       <c r="J21" s="23"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
@@ -1618,10 +1625,10 @@
       <c r="G24" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="25" t="s">
+      <c r="H24" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J24" s="23"/>
@@ -1655,8 +1662,8 @@
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="26"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="27"/>
       <c r="J25" s="23"/>
       <c r="L25" s="11" t="s">
         <v>5</v>
@@ -1698,8 +1705,8 @@
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="26"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="27"/>
       <c r="J26" s="23"/>
       <c r="L26" s="12" t="s">
         <v>15</v>
@@ -1723,8 +1730,8 @@
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="26"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="27"/>
       <c r="J27" s="23"/>
       <c r="L27" s="14" t="s">
         <v>17</v>
@@ -1754,8 +1761,8 @@
       <c r="E28" s="23"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="26"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="27"/>
       <c r="J28" s="23"/>
       <c r="L28" s="15" t="s">
         <v>23</v>
@@ -1783,7 +1790,7 @@
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="23" t="s">
@@ -1792,10 +1799,10 @@
       <c r="H29" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="27" t="s">
+      <c r="I29" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="28" t="s">
+      <c r="J29" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="9" t="s">
@@ -1826,11 +1833,11 @@
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
-      <c r="F30" s="29"/>
+      <c r="F30" s="24"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="25"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
@@ -1869,11 +1876,11 @@
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="29"/>
+      <c r="F31" s="24"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="25"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
@@ -1902,11 +1909,11 @@
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
-      <c r="F32" s="29"/>
+      <c r="F32" s="24"/>
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="25"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
@@ -1933,11 +1940,11 @@
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
-      <c r="F33" s="29"/>
+      <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="23"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="25"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
@@ -1962,19 +1969,19 @@
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="27" t="s">
+      <c r="G34" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="H34" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="24" t="s">
+      <c r="I34" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L34" s="9" t="s">
@@ -2005,11 +2012,11 @@
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="24"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="29"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
@@ -2048,11 +2055,11 @@
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="24"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="29"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
@@ -2081,11 +2088,11 @@
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="24"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="29"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
@@ -2112,11 +2119,11 @@
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
       <c r="E38" s="23"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="24"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="29"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
@@ -2149,11 +2156,11 @@
       <c r="F40" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="29" t="s">
+      <c r="G40" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="23"/>
-      <c r="I40" s="25" t="s">
+      <c r="I40" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J40" s="23"/>
@@ -2186,9 +2193,9 @@
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="F41" s="23"/>
-      <c r="G41" s="29"/>
+      <c r="G41" s="24"/>
       <c r="H41" s="23"/>
-      <c r="I41" s="26"/>
+      <c r="I41" s="27"/>
       <c r="J41" s="23"/>
       <c r="L41" s="11" t="s">
         <v>5</v>
@@ -2229,9 +2236,9 @@
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="F42" s="23"/>
-      <c r="G42" s="29"/>
+      <c r="G42" s="24"/>
       <c r="H42" s="23"/>
-      <c r="I42" s="26"/>
+      <c r="I42" s="27"/>
       <c r="J42" s="23"/>
       <c r="L42" s="12" t="s">
         <v>15</v>
@@ -2254,9 +2261,9 @@
       <c r="D43" s="23"/>
       <c r="E43" s="23"/>
       <c r="F43" s="23"/>
-      <c r="G43" s="29"/>
+      <c r="G43" s="24"/>
       <c r="H43" s="23"/>
-      <c r="I43" s="26"/>
+      <c r="I43" s="27"/>
       <c r="J43" s="23"/>
       <c r="L43" s="14" t="s">
         <v>17</v>
@@ -2285,9 +2292,9 @@
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
       <c r="F44" s="23"/>
-      <c r="G44" s="29"/>
+      <c r="G44" s="24"/>
       <c r="H44" s="23"/>
-      <c r="I44" s="26"/>
+      <c r="I44" s="27"/>
       <c r="J44" s="23"/>
       <c r="L44" s="15" t="s">
         <v>23</v>
@@ -2319,13 +2326,13 @@
       <c r="G45" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45" s="27" t="s">
+      <c r="H45" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J45" s="28" t="s">
+      <c r="J45" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="9" t="s">
@@ -2358,9 +2365,9 @@
       <c r="E46" s="23"/>
       <c r="F46" s="23"/>
       <c r="G46" s="23"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="28"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="25"/>
       <c r="L46" s="11" t="s">
         <v>5</v>
       </c>
@@ -2401,9 +2408,9 @@
       <c r="E47" s="23"/>
       <c r="F47" s="23"/>
       <c r="G47" s="23"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="28"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="25"/>
       <c r="L47" s="12" t="s">
         <v>15</v>
       </c>
@@ -2434,9 +2441,9 @@
       <c r="E48" s="23"/>
       <c r="F48" s="23"/>
       <c r="G48" s="23"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="28"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="25"/>
       <c r="L48" s="14" t="s">
         <v>17</v>
       </c>
@@ -2465,9 +2472,9 @@
       <c r="E49" s="23"/>
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="28"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="25"/>
       <c r="L49" s="15" t="s">
         <v>23</v>
       </c>
@@ -2492,19 +2499,19 @@
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23"/>
-      <c r="F50" s="27" t="s">
+      <c r="F50" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="27" t="s">
+      <c r="G50" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="27" t="s">
+      <c r="H50" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I50" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J50" s="24" t="s">
+      <c r="I50" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L50" s="9" t="s">
@@ -2535,11 +2542,11 @@
       <c r="C51" s="23"/>
       <c r="D51" s="23"/>
       <c r="E51" s="23"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="24"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="29"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
@@ -2578,11 +2585,11 @@
       <c r="C52" s="23"/>
       <c r="D52" s="23"/>
       <c r="E52" s="23"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="24"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="29"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
@@ -2611,11 +2618,11 @@
       <c r="C53" s="23"/>
       <c r="D53" s="23"/>
       <c r="E53" s="23"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="24"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="29"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
@@ -2642,11 +2649,11 @@
       <c r="C54" s="23"/>
       <c r="D54" s="23"/>
       <c r="E54" s="23"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="24"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="29"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
@@ -2676,14 +2683,14 @@
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="23"/>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="23"/>
       <c r="H56" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I56" s="25" t="s">
+      <c r="I56" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J56" s="23"/>
@@ -2715,10 +2722,10 @@
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
       <c r="E57" s="23"/>
-      <c r="F57" s="29"/>
+      <c r="F57" s="24"/>
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
-      <c r="I57" s="26"/>
+      <c r="I57" s="27"/>
       <c r="J57" s="23"/>
       <c r="L57" s="11" t="s">
         <v>5</v>
@@ -2758,10 +2765,10 @@
       <c r="C58" s="23"/>
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
-      <c r="F58" s="29"/>
+      <c r="F58" s="24"/>
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
-      <c r="I58" s="26"/>
+      <c r="I58" s="27"/>
       <c r="J58" s="23"/>
       <c r="L58" s="12" t="s">
         <v>15</v>
@@ -2783,10 +2790,10 @@
       <c r="C59" s="23"/>
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
-      <c r="F59" s="29"/>
+      <c r="F59" s="24"/>
       <c r="G59" s="23"/>
       <c r="H59" s="23"/>
-      <c r="I59" s="26"/>
+      <c r="I59" s="27"/>
       <c r="J59" s="23"/>
       <c r="L59" s="14" t="s">
         <v>17</v>
@@ -2814,10 +2821,10 @@
       <c r="C60" s="23"/>
       <c r="D60" s="23"/>
       <c r="E60" s="23"/>
-      <c r="F60" s="29"/>
+      <c r="F60" s="24"/>
       <c r="G60" s="23"/>
       <c r="H60" s="23"/>
-      <c r="I60" s="26"/>
+      <c r="I60" s="27"/>
       <c r="J60" s="23"/>
       <c r="L60" s="15" t="s">
         <v>23</v>
@@ -2846,16 +2853,16 @@
       <c r="F61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="29" t="s">
+      <c r="G61" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="27" t="s">
+      <c r="I61" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J61" s="28" t="s">
+      <c r="J61" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="9" t="s">
@@ -2887,10 +2894,10 @@
       <c r="D62" s="23"/>
       <c r="E62" s="23"/>
       <c r="F62" s="23"/>
-      <c r="G62" s="29"/>
+      <c r="G62" s="24"/>
       <c r="H62" s="23"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="25"/>
       <c r="L62" s="11" t="s">
         <v>5</v>
       </c>
@@ -2930,10 +2937,10 @@
       <c r="D63" s="23"/>
       <c r="E63" s="23"/>
       <c r="F63" s="23"/>
-      <c r="G63" s="29"/>
+      <c r="G63" s="24"/>
       <c r="H63" s="23"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="25"/>
       <c r="L63" s="12" t="s">
         <v>15</v>
       </c>
@@ -2963,10 +2970,10 @@
       <c r="D64" s="23"/>
       <c r="E64" s="23"/>
       <c r="F64" s="23"/>
-      <c r="G64" s="29"/>
+      <c r="G64" s="24"/>
       <c r="H64" s="23"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="25"/>
       <c r="L64" s="14" t="s">
         <v>17</v>
       </c>
@@ -2994,10 +3001,10 @@
       <c r="D65" s="23"/>
       <c r="E65" s="23"/>
       <c r="F65" s="23"/>
-      <c r="G65" s="29"/>
+      <c r="G65" s="24"/>
       <c r="H65" s="23"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="28"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="25"/>
       <c r="L65" s="15" t="s">
         <v>23</v>
       </c>
@@ -3022,19 +3029,19 @@
       </c>
       <c r="D66" s="23"/>
       <c r="E66" s="23"/>
-      <c r="F66" s="27" t="s">
+      <c r="F66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G66" s="27" t="s">
+      <c r="G66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H66" s="27" t="s">
+      <c r="H66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" s="24" t="s">
+      <c r="I66" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L66" s="9" t="s">
@@ -3065,11 +3072,11 @@
       <c r="C67" s="23"/>
       <c r="D67" s="23"/>
       <c r="E67" s="23"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="24"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="29"/>
       <c r="L67" s="11" t="s">
         <v>5</v>
       </c>
@@ -3108,11 +3115,11 @@
       <c r="C68" s="23"/>
       <c r="D68" s="23"/>
       <c r="E68" s="23"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="24"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="29"/>
       <c r="L68" s="12" t="s">
         <v>15</v>
       </c>
@@ -3141,11 +3148,11 @@
       <c r="C69" s="23"/>
       <c r="D69" s="23"/>
       <c r="E69" s="23"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="24"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="29"/>
       <c r="L69" s="14" t="s">
         <v>17</v>
       </c>
@@ -3172,11 +3179,11 @@
       <c r="C70" s="23"/>
       <c r="D70" s="23"/>
       <c r="E70" s="23"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="24"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="29"/>
       <c r="L70" s="15" t="s">
         <v>23</v>
       </c>
@@ -3231,10 +3238,10 @@
       <c r="G73" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H73" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I73" s="25" t="s">
+      <c r="H73" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J73" s="23"/>
@@ -3268,8 +3275,8 @@
       <c r="E74" s="23"/>
       <c r="F74" s="23"/>
       <c r="G74" s="23"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="26"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="27"/>
       <c r="J74" s="23"/>
       <c r="L74" s="11" t="s">
         <v>5</v>
@@ -3311,8 +3318,8 @@
       <c r="E75" s="23"/>
       <c r="F75" s="23"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="26"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="27"/>
       <c r="J75" s="23"/>
       <c r="L75" s="12" t="s">
         <v>15</v>
@@ -3336,8 +3343,8 @@
       <c r="E76" s="23"/>
       <c r="F76" s="23"/>
       <c r="G76" s="23"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="26"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="27"/>
       <c r="J76" s="23"/>
       <c r="L76" s="14" t="s">
         <v>17</v>
@@ -3367,8 +3374,8 @@
       <c r="E77" s="23"/>
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="26"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="27"/>
       <c r="J77" s="23"/>
       <c r="L77" s="15" t="s">
         <v>23</v>
@@ -3394,7 +3401,7 @@
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="23" t="s">
@@ -3403,10 +3410,10 @@
       <c r="H78" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I78" s="27" t="s">
+      <c r="I78" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J78" s="28" t="s">
+      <c r="J78" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L78" s="9" t="s">
@@ -3437,11 +3444,11 @@
       <c r="C79" s="23"/>
       <c r="D79" s="23"/>
       <c r="E79" s="23"/>
-      <c r="F79" s="29"/>
+      <c r="F79" s="24"/>
       <c r="G79" s="23"/>
       <c r="H79" s="23"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="28"/>
+      <c r="I79" s="28"/>
+      <c r="J79" s="25"/>
       <c r="L79" s="11" t="s">
         <v>5</v>
       </c>
@@ -3480,11 +3487,11 @@
       <c r="C80" s="23"/>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
-      <c r="F80" s="29"/>
+      <c r="F80" s="24"/>
       <c r="G80" s="23"/>
       <c r="H80" s="23"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="28"/>
+      <c r="I80" s="28"/>
+      <c r="J80" s="25"/>
       <c r="L80" s="12" t="s">
         <v>15</v>
       </c>
@@ -3513,11 +3520,11 @@
       <c r="C81" s="23"/>
       <c r="D81" s="23"/>
       <c r="E81" s="23"/>
-      <c r="F81" s="29"/>
+      <c r="F81" s="24"/>
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="25"/>
       <c r="L81" s="14" t="s">
         <v>17</v>
       </c>
@@ -3544,11 +3551,11 @@
       <c r="C82" s="23"/>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
-      <c r="F82" s="29"/>
+      <c r="F82" s="24"/>
       <c r="G82" s="23"/>
       <c r="H82" s="23"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="25"/>
       <c r="L82" s="15" t="s">
         <v>23</v>
       </c>
@@ -3573,19 +3580,19 @@
       </c>
       <c r="D83" s="23"/>
       <c r="E83" s="23"/>
-      <c r="F83" s="27" t="s">
+      <c r="F83" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G83" s="27" t="s">
+      <c r="G83" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H83" s="27" t="s">
+      <c r="H83" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I83" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J83" s="24" t="s">
+      <c r="I83" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L83" s="9" t="s">
@@ -3616,11 +3623,11 @@
       <c r="C84" s="23"/>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="28"/>
-      <c r="J84" s="24"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="29"/>
       <c r="L84" s="11" t="s">
         <v>5</v>
       </c>
@@ -3659,11 +3666,11 @@
       <c r="C85" s="23"/>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="28"/>
-      <c r="J85" s="24"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="28"/>
+      <c r="H85" s="28"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="29"/>
       <c r="L85" s="12" t="s">
         <v>15</v>
       </c>
@@ -3692,11 +3699,11 @@
       <c r="C86" s="23"/>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="27"/>
-      <c r="I86" s="28"/>
-      <c r="J86" s="24"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="28"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="29"/>
       <c r="L86" s="14" t="s">
         <v>17</v>
       </c>
@@ -3723,11 +3730,11 @@
       <c r="C87" s="23"/>
       <c r="D87" s="23"/>
       <c r="E87" s="23"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="27"/>
-      <c r="I87" s="28"/>
-      <c r="J87" s="24"/>
+      <c r="F87" s="28"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="25"/>
+      <c r="J87" s="29"/>
       <c r="L87" s="15" t="s">
         <v>23</v>
       </c>
@@ -3760,11 +3767,11 @@
       <c r="F89" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G89" s="29" t="s">
+      <c r="G89" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H89" s="23"/>
-      <c r="I89" s="25" t="s">
+      <c r="I89" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J89" s="23"/>
@@ -3797,9 +3804,9 @@
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
-      <c r="G90" s="29"/>
+      <c r="G90" s="24"/>
       <c r="H90" s="23"/>
-      <c r="I90" s="26"/>
+      <c r="I90" s="27"/>
       <c r="J90" s="23"/>
       <c r="L90" s="11" t="s">
         <v>5</v>
@@ -3840,9 +3847,9 @@
       <c r="D91" s="23"/>
       <c r="E91" s="23"/>
       <c r="F91" s="23"/>
-      <c r="G91" s="29"/>
+      <c r="G91" s="24"/>
       <c r="H91" s="23"/>
-      <c r="I91" s="26"/>
+      <c r="I91" s="27"/>
       <c r="J91" s="23"/>
       <c r="L91" s="12" t="s">
         <v>15</v>
@@ -3865,9 +3872,9 @@
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
-      <c r="G92" s="29"/>
+      <c r="G92" s="24"/>
       <c r="H92" s="23"/>
-      <c r="I92" s="26"/>
+      <c r="I92" s="27"/>
       <c r="J92" s="23"/>
       <c r="L92" s="14" t="s">
         <v>17</v>
@@ -3896,9 +3903,9 @@
       <c r="D93" s="23"/>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
-      <c r="G93" s="29"/>
+      <c r="G93" s="24"/>
       <c r="H93" s="23"/>
-      <c r="I93" s="26"/>
+      <c r="I93" s="27"/>
       <c r="J93" s="23"/>
       <c r="L93" s="15" t="s">
         <v>23</v>
@@ -3930,13 +3937,13 @@
       <c r="G94" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H94" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I94" s="27" t="s">
+      <c r="H94" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I94" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J94" s="28" t="s">
+      <c r="J94" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L94" s="9" t="s">
@@ -3969,9 +3976,9 @@
       <c r="E95" s="23"/>
       <c r="F95" s="23"/>
       <c r="G95" s="23"/>
-      <c r="H95" s="29"/>
-      <c r="I95" s="27"/>
-      <c r="J95" s="28"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="28"/>
+      <c r="J95" s="25"/>
       <c r="L95" s="11" t="s">
         <v>5</v>
       </c>
@@ -4012,9 +4019,9 @@
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
       <c r="G96" s="23"/>
-      <c r="H96" s="29"/>
-      <c r="I96" s="27"/>
-      <c r="J96" s="28"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="28"/>
+      <c r="J96" s="25"/>
       <c r="L96" s="12" t="s">
         <v>15</v>
       </c>
@@ -4045,9 +4052,9 @@
       <c r="E97" s="23"/>
       <c r="F97" s="23"/>
       <c r="G97" s="23"/>
-      <c r="H97" s="29"/>
-      <c r="I97" s="27"/>
-      <c r="J97" s="28"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="28"/>
+      <c r="J97" s="25"/>
       <c r="L97" s="14" t="s">
         <v>17</v>
       </c>
@@ -4076,9 +4083,9 @@
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
       <c r="G98" s="23"/>
-      <c r="H98" s="29"/>
-      <c r="I98" s="27"/>
-      <c r="J98" s="28"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="28"/>
+      <c r="J98" s="25"/>
       <c r="L98" s="15" t="s">
         <v>23</v>
       </c>
@@ -4103,19 +4110,19 @@
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23"/>
-      <c r="F99" s="27" t="s">
+      <c r="F99" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G99" s="27" t="s">
+      <c r="G99" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H99" s="27" t="s">
+      <c r="H99" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I99" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" s="24" t="s">
+      <c r="I99" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L99" s="9" t="s">
@@ -4146,11 +4153,11 @@
       <c r="C100" s="23"/>
       <c r="D100" s="23"/>
       <c r="E100" s="23"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="27"/>
-      <c r="H100" s="27"/>
-      <c r="I100" s="28"/>
-      <c r="J100" s="24"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="28"/>
+      <c r="H100" s="28"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="29"/>
       <c r="L100" s="11" t="s">
         <v>5</v>
       </c>
@@ -4189,11 +4196,11 @@
       <c r="C101" s="23"/>
       <c r="D101" s="23"/>
       <c r="E101" s="23"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
-      <c r="H101" s="27"/>
-      <c r="I101" s="28"/>
-      <c r="J101" s="24"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="29"/>
       <c r="L101" s="12" t="s">
         <v>15</v>
       </c>
@@ -4222,11 +4229,11 @@
       <c r="C102" s="23"/>
       <c r="D102" s="23"/>
       <c r="E102" s="23"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
-      <c r="H102" s="27"/>
-      <c r="I102" s="28"/>
-      <c r="J102" s="24"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="29"/>
       <c r="L102" s="14" t="s">
         <v>17</v>
       </c>
@@ -4253,11 +4260,11 @@
       <c r="C103" s="23"/>
       <c r="D103" s="23"/>
       <c r="E103" s="23"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="27"/>
-      <c r="I103" s="28"/>
-      <c r="J103" s="24"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="25"/>
+      <c r="J103" s="29"/>
       <c r="L103" s="15" t="s">
         <v>23</v>
       </c>
@@ -4285,14 +4292,14 @@
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23"/>
-      <c r="F105" s="29" t="s">
+      <c r="F105" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="23"/>
       <c r="H105" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I105" s="25" t="s">
+      <c r="I105" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J105" s="23"/>
@@ -4324,10 +4331,10 @@
       <c r="C106" s="23"/>
       <c r="D106" s="23"/>
       <c r="E106" s="23"/>
-      <c r="F106" s="29"/>
+      <c r="F106" s="24"/>
       <c r="G106" s="23"/>
       <c r="H106" s="23"/>
-      <c r="I106" s="26"/>
+      <c r="I106" s="27"/>
       <c r="J106" s="23"/>
       <c r="L106" s="11" t="s">
         <v>5</v>
@@ -4367,10 +4374,10 @@
       <c r="C107" s="23"/>
       <c r="D107" s="23"/>
       <c r="E107" s="23"/>
-      <c r="F107" s="29"/>
+      <c r="F107" s="24"/>
       <c r="G107" s="23"/>
       <c r="H107" s="23"/>
-      <c r="I107" s="26"/>
+      <c r="I107" s="27"/>
       <c r="J107" s="23"/>
       <c r="L107" s="12" t="s">
         <v>15</v>
@@ -4392,10 +4399,10 @@
       <c r="C108" s="23"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
-      <c r="F108" s="29"/>
+      <c r="F108" s="24"/>
       <c r="G108" s="23"/>
       <c r="H108" s="23"/>
-      <c r="I108" s="26"/>
+      <c r="I108" s="27"/>
       <c r="J108" s="23"/>
       <c r="L108" s="14" t="s">
         <v>17</v>
@@ -4423,10 +4430,10 @@
       <c r="C109" s="23"/>
       <c r="D109" s="23"/>
       <c r="E109" s="23"/>
-      <c r="F109" s="29"/>
+      <c r="F109" s="24"/>
       <c r="G109" s="23"/>
       <c r="H109" s="23"/>
-      <c r="I109" s="26"/>
+      <c r="I109" s="27"/>
       <c r="J109" s="23"/>
       <c r="L109" s="15" t="s">
         <v>23</v>
@@ -4455,16 +4462,16 @@
       <c r="F110" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="29" t="s">
+      <c r="G110" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H110" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I110" s="27" t="s">
+      <c r="I110" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J110" s="28" t="s">
+      <c r="J110" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L110" s="9" t="s">
@@ -4496,10 +4503,10 @@
       <c r="D111" s="23"/>
       <c r="E111" s="23"/>
       <c r="F111" s="23"/>
-      <c r="G111" s="29"/>
+      <c r="G111" s="24"/>
       <c r="H111" s="23"/>
-      <c r="I111" s="27"/>
-      <c r="J111" s="28"/>
+      <c r="I111" s="28"/>
+      <c r="J111" s="25"/>
       <c r="L111" s="11" t="s">
         <v>5</v>
       </c>
@@ -4539,10 +4546,10 @@
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
-      <c r="G112" s="29"/>
+      <c r="G112" s="24"/>
       <c r="H112" s="23"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="28"/>
+      <c r="I112" s="28"/>
+      <c r="J112" s="25"/>
       <c r="L112" s="12" t="s">
         <v>15</v>
       </c>
@@ -4572,10 +4579,10 @@
       <c r="D113" s="23"/>
       <c r="E113" s="23"/>
       <c r="F113" s="23"/>
-      <c r="G113" s="29"/>
+      <c r="G113" s="24"/>
       <c r="H113" s="23"/>
-      <c r="I113" s="27"/>
-      <c r="J113" s="28"/>
+      <c r="I113" s="28"/>
+      <c r="J113" s="25"/>
       <c r="L113" s="14" t="s">
         <v>17</v>
       </c>
@@ -4603,10 +4610,10 @@
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
-      <c r="G114" s="29"/>
+      <c r="G114" s="24"/>
       <c r="H114" s="23"/>
-      <c r="I114" s="27"/>
-      <c r="J114" s="28"/>
+      <c r="I114" s="28"/>
+      <c r="J114" s="25"/>
       <c r="L114" s="15" t="s">
         <v>23</v>
       </c>
@@ -4631,19 +4638,19 @@
       </c>
       <c r="D115" s="23"/>
       <c r="E115" s="23"/>
-      <c r="F115" s="27" t="s">
+      <c r="F115" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G115" s="27" t="s">
+      <c r="G115" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H115" s="27" t="s">
+      <c r="H115" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I115" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J115" s="24" t="s">
+      <c r="I115" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J115" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L115" s="9" t="s">
@@ -4674,11 +4681,11 @@
       <c r="C116" s="23"/>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="27"/>
-      <c r="H116" s="27"/>
-      <c r="I116" s="28"/>
-      <c r="J116" s="24"/>
+      <c r="F116" s="28"/>
+      <c r="G116" s="28"/>
+      <c r="H116" s="28"/>
+      <c r="I116" s="25"/>
+      <c r="J116" s="29"/>
       <c r="L116" s="11" t="s">
         <v>5</v>
       </c>
@@ -4717,11 +4724,11 @@
       <c r="C117" s="23"/>
       <c r="D117" s="23"/>
       <c r="E117" s="23"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="27"/>
-      <c r="H117" s="27"/>
-      <c r="I117" s="28"/>
-      <c r="J117" s="24"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="28"/>
+      <c r="H117" s="28"/>
+      <c r="I117" s="25"/>
+      <c r="J117" s="29"/>
       <c r="L117" s="12" t="s">
         <v>15</v>
       </c>
@@ -4750,11 +4757,11 @@
       <c r="C118" s="23"/>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
-      <c r="F118" s="27"/>
-      <c r="G118" s="27"/>
-      <c r="H118" s="27"/>
-      <c r="I118" s="28"/>
-      <c r="J118" s="24"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="29"/>
       <c r="L118" s="14" t="s">
         <v>17</v>
       </c>
@@ -4781,11 +4788,11 @@
       <c r="C119" s="23"/>
       <c r="D119" s="23"/>
       <c r="E119" s="23"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="27"/>
-      <c r="H119" s="27"/>
-      <c r="I119" s="28"/>
-      <c r="J119" s="24"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="28"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="25"/>
+      <c r="J119" s="29"/>
       <c r="L119" s="15" t="s">
         <v>23</v>
       </c>
@@ -4823,10 +4830,10 @@
       <c r="G122" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H122" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I122" s="25" t="s">
+      <c r="H122" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I122" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J122" s="23"/>
@@ -4860,8 +4867,8 @@
       <c r="E123" s="23"/>
       <c r="F123" s="23"/>
       <c r="G123" s="23"/>
-      <c r="H123" s="29"/>
-      <c r="I123" s="26"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="27"/>
       <c r="J123" s="23"/>
       <c r="L123" s="11" t="s">
         <v>5</v>
@@ -4903,8 +4910,8 @@
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
       <c r="G124" s="23"/>
-      <c r="H124" s="29"/>
-      <c r="I124" s="26"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="27"/>
       <c r="J124" s="23"/>
       <c r="L124" s="12" t="s">
         <v>15</v>
@@ -4928,8 +4935,8 @@
       <c r="E125" s="23"/>
       <c r="F125" s="23"/>
       <c r="G125" s="23"/>
-      <c r="H125" s="29"/>
-      <c r="I125" s="26"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="27"/>
       <c r="J125" s="23"/>
       <c r="L125" s="14" t="s">
         <v>17</v>
@@ -4959,8 +4966,8 @@
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
       <c r="G126" s="23"/>
-      <c r="H126" s="29"/>
-      <c r="I126" s="26"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="27"/>
       <c r="J126" s="23"/>
       <c r="L126" s="15" t="s">
         <v>23</v>
@@ -4986,7 +4993,7 @@
       </c>
       <c r="D127" s="23"/>
       <c r="E127" s="23"/>
-      <c r="F127" s="29" t="s">
+      <c r="F127" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="23" t="s">
@@ -4995,10 +5002,10 @@
       <c r="H127" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I127" s="27" t="s">
+      <c r="I127" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J127" s="28" t="s">
+      <c r="J127" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L127" s="9" t="s">
@@ -5029,11 +5036,11 @@
       <c r="C128" s="23"/>
       <c r="D128" s="23"/>
       <c r="E128" s="23"/>
-      <c r="F128" s="29"/>
+      <c r="F128" s="24"/>
       <c r="G128" s="23"/>
       <c r="H128" s="23"/>
-      <c r="I128" s="27"/>
-      <c r="J128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="25"/>
       <c r="L128" s="11" t="s">
         <v>5</v>
       </c>
@@ -5072,11 +5079,11 @@
       <c r="C129" s="23"/>
       <c r="D129" s="23"/>
       <c r="E129" s="23"/>
-      <c r="F129" s="29"/>
+      <c r="F129" s="24"/>
       <c r="G129" s="23"/>
       <c r="H129" s="23"/>
-      <c r="I129" s="27"/>
-      <c r="J129" s="28"/>
+      <c r="I129" s="28"/>
+      <c r="J129" s="25"/>
       <c r="L129" s="12" t="s">
         <v>15</v>
       </c>
@@ -5105,11 +5112,11 @@
       <c r="C130" s="23"/>
       <c r="D130" s="23"/>
       <c r="E130" s="23"/>
-      <c r="F130" s="29"/>
+      <c r="F130" s="24"/>
       <c r="G130" s="23"/>
       <c r="H130" s="23"/>
-      <c r="I130" s="27"/>
-      <c r="J130" s="28"/>
+      <c r="I130" s="28"/>
+      <c r="J130" s="25"/>
       <c r="L130" s="14" t="s">
         <v>17</v>
       </c>
@@ -5136,11 +5143,11 @@
       <c r="C131" s="23"/>
       <c r="D131" s="23"/>
       <c r="E131" s="23"/>
-      <c r="F131" s="29"/>
+      <c r="F131" s="24"/>
       <c r="G131" s="23"/>
       <c r="H131" s="23"/>
-      <c r="I131" s="27"/>
-      <c r="J131" s="28"/>
+      <c r="I131" s="28"/>
+      <c r="J131" s="25"/>
       <c r="L131" s="15" t="s">
         <v>23</v>
       </c>
@@ -5165,19 +5172,19 @@
       </c>
       <c r="D132" s="23"/>
       <c r="E132" s="23"/>
-      <c r="F132" s="27" t="s">
+      <c r="F132" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G132" s="27" t="s">
+      <c r="G132" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H132" s="27" t="s">
+      <c r="H132" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I132" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J132" s="24" t="s">
+      <c r="I132" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J132" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L132" s="9" t="s">
@@ -5208,11 +5215,11 @@
       <c r="C133" s="23"/>
       <c r="D133" s="23"/>
       <c r="E133" s="23"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="27"/>
-      <c r="H133" s="27"/>
-      <c r="I133" s="28"/>
-      <c r="J133" s="24"/>
+      <c r="F133" s="28"/>
+      <c r="G133" s="28"/>
+      <c r="H133" s="28"/>
+      <c r="I133" s="25"/>
+      <c r="J133" s="29"/>
       <c r="L133" s="11" t="s">
         <v>5</v>
       </c>
@@ -5251,11 +5258,11 @@
       <c r="C134" s="23"/>
       <c r="D134" s="23"/>
       <c r="E134" s="23"/>
-      <c r="F134" s="27"/>
-      <c r="G134" s="27"/>
-      <c r="H134" s="27"/>
-      <c r="I134" s="28"/>
-      <c r="J134" s="24"/>
+      <c r="F134" s="28"/>
+      <c r="G134" s="28"/>
+      <c r="H134" s="28"/>
+      <c r="I134" s="25"/>
+      <c r="J134" s="29"/>
       <c r="L134" s="12" t="s">
         <v>15</v>
       </c>
@@ -5284,11 +5291,11 @@
       <c r="C135" s="23"/>
       <c r="D135" s="23"/>
       <c r="E135" s="23"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="27"/>
-      <c r="H135" s="27"/>
-      <c r="I135" s="28"/>
-      <c r="J135" s="24"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="29"/>
       <c r="L135" s="14" t="s">
         <v>17</v>
       </c>
@@ -5315,11 +5322,11 @@
       <c r="C136" s="23"/>
       <c r="D136" s="23"/>
       <c r="E136" s="23"/>
-      <c r="F136" s="27"/>
-      <c r="G136" s="27"/>
-      <c r="H136" s="27"/>
-      <c r="I136" s="28"/>
-      <c r="J136" s="24"/>
+      <c r="F136" s="28"/>
+      <c r="G136" s="28"/>
+      <c r="H136" s="28"/>
+      <c r="I136" s="25"/>
+      <c r="J136" s="29"/>
       <c r="L136" s="15" t="s">
         <v>23</v>
       </c>
@@ -5350,11 +5357,11 @@
       <c r="F138" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G138" s="29" t="s">
+      <c r="G138" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H138" s="23"/>
-      <c r="I138" s="25" t="s">
+      <c r="I138" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J138" s="23"/>
@@ -5387,9 +5394,9 @@
       <c r="D139" s="23"/>
       <c r="E139" s="23"/>
       <c r="F139" s="23"/>
-      <c r="G139" s="29"/>
+      <c r="G139" s="24"/>
       <c r="H139" s="23"/>
-      <c r="I139" s="26"/>
+      <c r="I139" s="27"/>
       <c r="J139" s="23"/>
       <c r="L139" s="11" t="s">
         <v>5</v>
@@ -5430,9 +5437,9 @@
       <c r="D140" s="23"/>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
-      <c r="G140" s="29"/>
+      <c r="G140" s="24"/>
       <c r="H140" s="23"/>
-      <c r="I140" s="26"/>
+      <c r="I140" s="27"/>
       <c r="J140" s="23"/>
       <c r="L140" s="12" t="s">
         <v>15</v>
@@ -5455,9 +5462,9 @@
       <c r="D141" s="23"/>
       <c r="E141" s="23"/>
       <c r="F141" s="23"/>
-      <c r="G141" s="29"/>
+      <c r="G141" s="24"/>
       <c r="H141" s="23"/>
-      <c r="I141" s="26"/>
+      <c r="I141" s="27"/>
       <c r="J141" s="23"/>
       <c r="L141" s="14" t="s">
         <v>17</v>
@@ -5486,9 +5493,9 @@
       <c r="D142" s="23"/>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
-      <c r="G142" s="29"/>
+      <c r="G142" s="24"/>
       <c r="H142" s="23"/>
-      <c r="I142" s="26"/>
+      <c r="I142" s="27"/>
       <c r="J142" s="23"/>
       <c r="L142" s="15" t="s">
         <v>23</v>
@@ -5520,13 +5527,13 @@
       <c r="G143" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H143" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I143" s="27" t="s">
+      <c r="H143" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I143" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J143" s="28" t="s">
+      <c r="J143" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L143" s="9" t="s">
@@ -5559,9 +5566,9 @@
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
       <c r="G144" s="23"/>
-      <c r="H144" s="29"/>
-      <c r="I144" s="27"/>
-      <c r="J144" s="28"/>
+      <c r="H144" s="24"/>
+      <c r="I144" s="28"/>
+      <c r="J144" s="25"/>
       <c r="L144" s="11" t="s">
         <v>5</v>
       </c>
@@ -5602,9 +5609,9 @@
       <c r="E145" s="23"/>
       <c r="F145" s="23"/>
       <c r="G145" s="23"/>
-      <c r="H145" s="29"/>
-      <c r="I145" s="27"/>
-      <c r="J145" s="28"/>
+      <c r="H145" s="24"/>
+      <c r="I145" s="28"/>
+      <c r="J145" s="25"/>
       <c r="L145" s="12" t="s">
         <v>15</v>
       </c>
@@ -5635,9 +5642,9 @@
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
       <c r="G146" s="23"/>
-      <c r="H146" s="29"/>
-      <c r="I146" s="27"/>
-      <c r="J146" s="28"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="28"/>
+      <c r="J146" s="25"/>
       <c r="L146" s="14" t="s">
         <v>17</v>
       </c>
@@ -5666,9 +5673,9 @@
       <c r="E147" s="23"/>
       <c r="F147" s="23"/>
       <c r="G147" s="23"/>
-      <c r="H147" s="29"/>
-      <c r="I147" s="27"/>
-      <c r="J147" s="28"/>
+      <c r="H147" s="24"/>
+      <c r="I147" s="28"/>
+      <c r="J147" s="25"/>
       <c r="L147" s="15" t="s">
         <v>23</v>
       </c>
@@ -5693,19 +5700,19 @@
       </c>
       <c r="D148" s="23"/>
       <c r="E148" s="23"/>
-      <c r="F148" s="27" t="s">
+      <c r="F148" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G148" s="27" t="s">
+      <c r="G148" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H148" s="27" t="s">
+      <c r="H148" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I148" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J148" s="24" t="s">
+      <c r="I148" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J148" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L148" s="9" t="s">
@@ -5736,11 +5743,11 @@
       <c r="C149" s="23"/>
       <c r="D149" s="23"/>
       <c r="E149" s="23"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="28"/>
-      <c r="J149" s="24"/>
+      <c r="F149" s="28"/>
+      <c r="G149" s="28"/>
+      <c r="H149" s="28"/>
+      <c r="I149" s="25"/>
+      <c r="J149" s="29"/>
       <c r="L149" s="11" t="s">
         <v>5</v>
       </c>
@@ -5779,11 +5786,11 @@
       <c r="C150" s="23"/>
       <c r="D150" s="23"/>
       <c r="E150" s="23"/>
-      <c r="F150" s="27"/>
-      <c r="G150" s="27"/>
-      <c r="H150" s="27"/>
-      <c r="I150" s="28"/>
-      <c r="J150" s="24"/>
+      <c r="F150" s="28"/>
+      <c r="G150" s="28"/>
+      <c r="H150" s="28"/>
+      <c r="I150" s="25"/>
+      <c r="J150" s="29"/>
       <c r="L150" s="12" t="s">
         <v>15</v>
       </c>
@@ -5812,11 +5819,11 @@
       <c r="C151" s="23"/>
       <c r="D151" s="23"/>
       <c r="E151" s="23"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="27"/>
-      <c r="H151" s="27"/>
-      <c r="I151" s="28"/>
-      <c r="J151" s="24"/>
+      <c r="F151" s="28"/>
+      <c r="G151" s="28"/>
+      <c r="H151" s="28"/>
+      <c r="I151" s="25"/>
+      <c r="J151" s="29"/>
       <c r="L151" s="14" t="s">
         <v>17</v>
       </c>
@@ -5843,11 +5850,11 @@
       <c r="C152" s="23"/>
       <c r="D152" s="23"/>
       <c r="E152" s="23"/>
-      <c r="F152" s="27"/>
-      <c r="G152" s="27"/>
-      <c r="H152" s="27"/>
-      <c r="I152" s="28"/>
-      <c r="J152" s="24"/>
+      <c r="F152" s="28"/>
+      <c r="G152" s="28"/>
+      <c r="H152" s="28"/>
+      <c r="I152" s="25"/>
+      <c r="J152" s="29"/>
       <c r="L152" s="15" t="s">
         <v>23</v>
       </c>
@@ -5875,14 +5882,14 @@
       </c>
       <c r="D154" s="23"/>
       <c r="E154" s="23"/>
-      <c r="F154" s="29" t="s">
+      <c r="F154" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="23"/>
       <c r="H154" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I154" s="25" t="s">
+      <c r="I154" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J154" s="23"/>
@@ -5914,10 +5921,10 @@
       <c r="C155" s="23"/>
       <c r="D155" s="23"/>
       <c r="E155" s="23"/>
-      <c r="F155" s="29"/>
+      <c r="F155" s="24"/>
       <c r="G155" s="23"/>
       <c r="H155" s="23"/>
-      <c r="I155" s="26"/>
+      <c r="I155" s="27"/>
       <c r="J155" s="23"/>
       <c r="L155" s="11" t="s">
         <v>5</v>
@@ -5957,10 +5964,10 @@
       <c r="C156" s="23"/>
       <c r="D156" s="23"/>
       <c r="E156" s="23"/>
-      <c r="F156" s="29"/>
+      <c r="F156" s="24"/>
       <c r="G156" s="23"/>
       <c r="H156" s="23"/>
-      <c r="I156" s="26"/>
+      <c r="I156" s="27"/>
       <c r="J156" s="23"/>
       <c r="L156" s="12" t="s">
         <v>15</v>
@@ -5982,10 +5989,10 @@
       <c r="C157" s="23"/>
       <c r="D157" s="23"/>
       <c r="E157" s="23"/>
-      <c r="F157" s="29"/>
+      <c r="F157" s="24"/>
       <c r="G157" s="23"/>
       <c r="H157" s="23"/>
-      <c r="I157" s="26"/>
+      <c r="I157" s="27"/>
       <c r="J157" s="23"/>
       <c r="L157" s="14" t="s">
         <v>17</v>
@@ -6013,10 +6020,10 @@
       <c r="C158" s="23"/>
       <c r="D158" s="23"/>
       <c r="E158" s="23"/>
-      <c r="F158" s="29"/>
+      <c r="F158" s="24"/>
       <c r="G158" s="23"/>
       <c r="H158" s="23"/>
-      <c r="I158" s="26"/>
+      <c r="I158" s="27"/>
       <c r="J158" s="23"/>
       <c r="L158" s="15" t="s">
         <v>23</v>
@@ -6045,16 +6052,16 @@
       <c r="F159" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="29" t="s">
+      <c r="G159" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H159" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I159" s="27" t="s">
+      <c r="I159" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J159" s="28" t="s">
+      <c r="J159" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L159" s="9" t="s">
@@ -6086,10 +6093,10 @@
       <c r="D160" s="23"/>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
-      <c r="G160" s="29"/>
+      <c r="G160" s="24"/>
       <c r="H160" s="23"/>
-      <c r="I160" s="27"/>
-      <c r="J160" s="28"/>
+      <c r="I160" s="28"/>
+      <c r="J160" s="25"/>
       <c r="L160" s="11" t="s">
         <v>5</v>
       </c>
@@ -6129,10 +6136,10 @@
       <c r="D161" s="23"/>
       <c r="E161" s="23"/>
       <c r="F161" s="23"/>
-      <c r="G161" s="29"/>
+      <c r="G161" s="24"/>
       <c r="H161" s="23"/>
-      <c r="I161" s="27"/>
-      <c r="J161" s="28"/>
+      <c r="I161" s="28"/>
+      <c r="J161" s="25"/>
       <c r="L161" s="12" t="s">
         <v>15</v>
       </c>
@@ -6162,10 +6169,10 @@
       <c r="D162" s="23"/>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
-      <c r="G162" s="29"/>
+      <c r="G162" s="24"/>
       <c r="H162" s="23"/>
-      <c r="I162" s="27"/>
-      <c r="J162" s="28"/>
+      <c r="I162" s="28"/>
+      <c r="J162" s="25"/>
       <c r="L162" s="14" t="s">
         <v>17</v>
       </c>
@@ -6193,10 +6200,10 @@
       <c r="D163" s="23"/>
       <c r="E163" s="23"/>
       <c r="F163" s="23"/>
-      <c r="G163" s="29"/>
+      <c r="G163" s="24"/>
       <c r="H163" s="23"/>
-      <c r="I163" s="27"/>
-      <c r="J163" s="28"/>
+      <c r="I163" s="28"/>
+      <c r="J163" s="25"/>
       <c r="L163" s="15" t="s">
         <v>23</v>
       </c>
@@ -6221,19 +6228,19 @@
       </c>
       <c r="D164" s="23"/>
       <c r="E164" s="23"/>
-      <c r="F164" s="27" t="s">
+      <c r="F164" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G164" s="27" t="s">
+      <c r="G164" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H164" s="27" t="s">
+      <c r="H164" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I164" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J164" s="24" t="s">
+      <c r="I164" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J164" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L164" s="9" t="s">
@@ -6264,11 +6271,11 @@
       <c r="C165" s="23"/>
       <c r="D165" s="23"/>
       <c r="E165" s="23"/>
-      <c r="F165" s="27"/>
-      <c r="G165" s="27"/>
-      <c r="H165" s="27"/>
-      <c r="I165" s="28"/>
-      <c r="J165" s="24"/>
+      <c r="F165" s="28"/>
+      <c r="G165" s="28"/>
+      <c r="H165" s="28"/>
+      <c r="I165" s="25"/>
+      <c r="J165" s="29"/>
       <c r="L165" s="11" t="s">
         <v>5</v>
       </c>
@@ -6307,11 +6314,11 @@
       <c r="C166" s="23"/>
       <c r="D166" s="23"/>
       <c r="E166" s="23"/>
-      <c r="F166" s="27"/>
-      <c r="G166" s="27"/>
-      <c r="H166" s="27"/>
-      <c r="I166" s="28"/>
-      <c r="J166" s="24"/>
+      <c r="F166" s="28"/>
+      <c r="G166" s="28"/>
+      <c r="H166" s="28"/>
+      <c r="I166" s="25"/>
+      <c r="J166" s="29"/>
       <c r="L166" s="12" t="s">
         <v>15</v>
       </c>
@@ -6340,11 +6347,11 @@
       <c r="C167" s="23"/>
       <c r="D167" s="23"/>
       <c r="E167" s="23"/>
-      <c r="F167" s="27"/>
-      <c r="G167" s="27"/>
-      <c r="H167" s="27"/>
-      <c r="I167" s="28"/>
-      <c r="J167" s="24"/>
+      <c r="F167" s="28"/>
+      <c r="G167" s="28"/>
+      <c r="H167" s="28"/>
+      <c r="I167" s="25"/>
+      <c r="J167" s="29"/>
       <c r="L167" s="14" t="s">
         <v>17</v>
       </c>
@@ -6371,11 +6378,11 @@
       <c r="C168" s="23"/>
       <c r="D168" s="23"/>
       <c r="E168" s="23"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="27"/>
-      <c r="H168" s="27"/>
-      <c r="I168" s="28"/>
-      <c r="J168" s="24"/>
+      <c r="F168" s="28"/>
+      <c r="G168" s="28"/>
+      <c r="H168" s="28"/>
+      <c r="I168" s="25"/>
+      <c r="J168" s="29"/>
       <c r="L168" s="15" t="s">
         <v>23</v>
       </c>
@@ -6428,10 +6435,10 @@
       <c r="G171" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H171" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I171" s="25" t="s">
+      <c r="H171" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I171" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J171" s="23"/>
@@ -6465,8 +6472,8 @@
       <c r="E172" s="23"/>
       <c r="F172" s="23"/>
       <c r="G172" s="23"/>
-      <c r="H172" s="29"/>
-      <c r="I172" s="26"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="27"/>
       <c r="J172" s="23"/>
       <c r="L172" s="11" t="s">
         <v>5</v>
@@ -6508,8 +6515,8 @@
       <c r="E173" s="23"/>
       <c r="F173" s="23"/>
       <c r="G173" s="23"/>
-      <c r="H173" s="29"/>
-      <c r="I173" s="26"/>
+      <c r="H173" s="24"/>
+      <c r="I173" s="27"/>
       <c r="J173" s="23"/>
       <c r="L173" s="12" t="s">
         <v>15</v>
@@ -6533,8 +6540,8 @@
       <c r="E174" s="23"/>
       <c r="F174" s="23"/>
       <c r="G174" s="23"/>
-      <c r="H174" s="29"/>
-      <c r="I174" s="26"/>
+      <c r="H174" s="24"/>
+      <c r="I174" s="27"/>
       <c r="J174" s="23"/>
       <c r="L174" s="14" t="s">
         <v>17</v>
@@ -6564,8 +6571,8 @@
       <c r="E175" s="23"/>
       <c r="F175" s="23"/>
       <c r="G175" s="23"/>
-      <c r="H175" s="29"/>
-      <c r="I175" s="26"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="27"/>
       <c r="J175" s="23"/>
       <c r="L175" s="15" t="s">
         <v>23</v>
@@ -6591,7 +6598,7 @@
       </c>
       <c r="D176" s="23"/>
       <c r="E176" s="23"/>
-      <c r="F176" s="29" t="s">
+      <c r="F176" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="23" t="s">
@@ -6600,10 +6607,10 @@
       <c r="H176" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I176" s="27" t="s">
+      <c r="I176" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J176" s="28" t="s">
+      <c r="J176" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L176" s="9" t="s">
@@ -6634,11 +6641,11 @@
       <c r="C177" s="23"/>
       <c r="D177" s="23"/>
       <c r="E177" s="23"/>
-      <c r="F177" s="29"/>
+      <c r="F177" s="24"/>
       <c r="G177" s="23"/>
       <c r="H177" s="23"/>
-      <c r="I177" s="27"/>
-      <c r="J177" s="28"/>
+      <c r="I177" s="28"/>
+      <c r="J177" s="25"/>
       <c r="L177" s="11" t="s">
         <v>5</v>
       </c>
@@ -6677,11 +6684,11 @@
       <c r="C178" s="23"/>
       <c r="D178" s="23"/>
       <c r="E178" s="23"/>
-      <c r="F178" s="29"/>
+      <c r="F178" s="24"/>
       <c r="G178" s="23"/>
       <c r="H178" s="23"/>
-      <c r="I178" s="27"/>
-      <c r="J178" s="28"/>
+      <c r="I178" s="28"/>
+      <c r="J178" s="25"/>
       <c r="L178" s="12" t="s">
         <v>15</v>
       </c>
@@ -6710,11 +6717,11 @@
       <c r="C179" s="23"/>
       <c r="D179" s="23"/>
       <c r="E179" s="23"/>
-      <c r="F179" s="29"/>
+      <c r="F179" s="24"/>
       <c r="G179" s="23"/>
       <c r="H179" s="23"/>
-      <c r="I179" s="27"/>
-      <c r="J179" s="28"/>
+      <c r="I179" s="28"/>
+      <c r="J179" s="25"/>
       <c r="L179" s="14" t="s">
         <v>17</v>
       </c>
@@ -6741,11 +6748,11 @@
       <c r="C180" s="23"/>
       <c r="D180" s="23"/>
       <c r="E180" s="23"/>
-      <c r="F180" s="29"/>
+      <c r="F180" s="24"/>
       <c r="G180" s="23"/>
       <c r="H180" s="23"/>
-      <c r="I180" s="27"/>
-      <c r="J180" s="28"/>
+      <c r="I180" s="28"/>
+      <c r="J180" s="25"/>
       <c r="L180" s="15" t="s">
         <v>23</v>
       </c>
@@ -6770,19 +6777,19 @@
       </c>
       <c r="D181" s="23"/>
       <c r="E181" s="23"/>
-      <c r="F181" s="27" t="s">
+      <c r="F181" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G181" s="27" t="s">
+      <c r="G181" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H181" s="27" t="s">
+      <c r="H181" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I181" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J181" s="24" t="s">
+      <c r="I181" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J181" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L181" s="9" t="s">
@@ -6813,11 +6820,11 @@
       <c r="C182" s="23"/>
       <c r="D182" s="23"/>
       <c r="E182" s="23"/>
-      <c r="F182" s="27"/>
-      <c r="G182" s="27"/>
-      <c r="H182" s="27"/>
-      <c r="I182" s="28"/>
-      <c r="J182" s="24"/>
+      <c r="F182" s="28"/>
+      <c r="G182" s="28"/>
+      <c r="H182" s="28"/>
+      <c r="I182" s="25"/>
+      <c r="J182" s="29"/>
       <c r="L182" s="11" t="s">
         <v>5</v>
       </c>
@@ -6856,11 +6863,11 @@
       <c r="C183" s="23"/>
       <c r="D183" s="23"/>
       <c r="E183" s="23"/>
-      <c r="F183" s="27"/>
-      <c r="G183" s="27"/>
-      <c r="H183" s="27"/>
-      <c r="I183" s="28"/>
-      <c r="J183" s="24"/>
+      <c r="F183" s="28"/>
+      <c r="G183" s="28"/>
+      <c r="H183" s="28"/>
+      <c r="I183" s="25"/>
+      <c r="J183" s="29"/>
       <c r="L183" s="12" t="s">
         <v>15</v>
       </c>
@@ -6889,11 +6896,11 @@
       <c r="C184" s="23"/>
       <c r="D184" s="23"/>
       <c r="E184" s="23"/>
-      <c r="F184" s="27"/>
-      <c r="G184" s="27"/>
-      <c r="H184" s="27"/>
-      <c r="I184" s="28"/>
-      <c r="J184" s="24"/>
+      <c r="F184" s="28"/>
+      <c r="G184" s="28"/>
+      <c r="H184" s="28"/>
+      <c r="I184" s="25"/>
+      <c r="J184" s="29"/>
       <c r="L184" s="14" t="s">
         <v>17</v>
       </c>
@@ -6920,11 +6927,11 @@
       <c r="C185" s="23"/>
       <c r="D185" s="23"/>
       <c r="E185" s="23"/>
-      <c r="F185" s="27"/>
-      <c r="G185" s="27"/>
-      <c r="H185" s="27"/>
-      <c r="I185" s="28"/>
-      <c r="J185" s="24"/>
+      <c r="F185" s="28"/>
+      <c r="G185" s="28"/>
+      <c r="H185" s="28"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="29"/>
       <c r="L185" s="15" t="s">
         <v>23</v>
       </c>
@@ -6955,11 +6962,11 @@
       <c r="F187" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G187" s="29" t="s">
+      <c r="G187" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H187" s="23"/>
-      <c r="I187" s="25" t="s">
+      <c r="I187" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J187" s="23"/>
@@ -6992,9 +6999,9 @@
       <c r="D188" s="23"/>
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
-      <c r="G188" s="29"/>
+      <c r="G188" s="24"/>
       <c r="H188" s="23"/>
-      <c r="I188" s="26"/>
+      <c r="I188" s="27"/>
       <c r="J188" s="23"/>
       <c r="L188" s="11" t="s">
         <v>5</v>
@@ -7035,9 +7042,9 @@
       <c r="D189" s="23"/>
       <c r="E189" s="23"/>
       <c r="F189" s="23"/>
-      <c r="G189" s="29"/>
+      <c r="G189" s="24"/>
       <c r="H189" s="23"/>
-      <c r="I189" s="26"/>
+      <c r="I189" s="27"/>
       <c r="J189" s="23"/>
       <c r="L189" s="12" t="s">
         <v>15</v>
@@ -7060,9 +7067,9 @@
       <c r="D190" s="23"/>
       <c r="E190" s="23"/>
       <c r="F190" s="23"/>
-      <c r="G190" s="29"/>
+      <c r="G190" s="24"/>
       <c r="H190" s="23"/>
-      <c r="I190" s="26"/>
+      <c r="I190" s="27"/>
       <c r="J190" s="23"/>
       <c r="L190" s="14" t="s">
         <v>17</v>
@@ -7091,9 +7098,9 @@
       <c r="D191" s="23"/>
       <c r="E191" s="23"/>
       <c r="F191" s="23"/>
-      <c r="G191" s="29"/>
+      <c r="G191" s="24"/>
       <c r="H191" s="23"/>
-      <c r="I191" s="26"/>
+      <c r="I191" s="27"/>
       <c r="J191" s="23"/>
       <c r="L191" s="15" t="s">
         <v>23</v>
@@ -7125,13 +7132,13 @@
       <c r="G192" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H192" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I192" s="27" t="s">
+      <c r="H192" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I192" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J192" s="28" t="s">
+      <c r="J192" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L192" s="9" t="s">
@@ -7164,9 +7171,9 @@
       <c r="E193" s="23"/>
       <c r="F193" s="23"/>
       <c r="G193" s="23"/>
-      <c r="H193" s="29"/>
-      <c r="I193" s="27"/>
-      <c r="J193" s="28"/>
+      <c r="H193" s="24"/>
+      <c r="I193" s="28"/>
+      <c r="J193" s="25"/>
       <c r="L193" s="11" t="s">
         <v>5</v>
       </c>
@@ -7207,9 +7214,9 @@
       <c r="E194" s="23"/>
       <c r="F194" s="23"/>
       <c r="G194" s="23"/>
-      <c r="H194" s="29"/>
-      <c r="I194" s="27"/>
-      <c r="J194" s="28"/>
+      <c r="H194" s="24"/>
+      <c r="I194" s="28"/>
+      <c r="J194" s="25"/>
       <c r="L194" s="12" t="s">
         <v>15</v>
       </c>
@@ -7240,9 +7247,9 @@
       <c r="E195" s="23"/>
       <c r="F195" s="23"/>
       <c r="G195" s="23"/>
-      <c r="H195" s="29"/>
-      <c r="I195" s="27"/>
-      <c r="J195" s="28"/>
+      <c r="H195" s="24"/>
+      <c r="I195" s="28"/>
+      <c r="J195" s="25"/>
       <c r="L195" s="14" t="s">
         <v>17</v>
       </c>
@@ -7271,9 +7278,9 @@
       <c r="E196" s="23"/>
       <c r="F196" s="23"/>
       <c r="G196" s="23"/>
-      <c r="H196" s="29"/>
-      <c r="I196" s="27"/>
-      <c r="J196" s="28"/>
+      <c r="H196" s="24"/>
+      <c r="I196" s="28"/>
+      <c r="J196" s="25"/>
       <c r="L196" s="15" t="s">
         <v>23</v>
       </c>
@@ -7298,19 +7305,19 @@
       </c>
       <c r="D197" s="23"/>
       <c r="E197" s="23"/>
-      <c r="F197" s="27" t="s">
+      <c r="F197" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G197" s="27" t="s">
+      <c r="G197" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H197" s="27" t="s">
+      <c r="H197" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I197" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J197" s="24" t="s">
+      <c r="I197" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J197" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L197" s="9" t="s">
@@ -7341,11 +7348,11 @@
       <c r="C198" s="23"/>
       <c r="D198" s="23"/>
       <c r="E198" s="23"/>
-      <c r="F198" s="27"/>
-      <c r="G198" s="27"/>
-      <c r="H198" s="27"/>
-      <c r="I198" s="28"/>
-      <c r="J198" s="24"/>
+      <c r="F198" s="28"/>
+      <c r="G198" s="28"/>
+      <c r="H198" s="28"/>
+      <c r="I198" s="25"/>
+      <c r="J198" s="29"/>
       <c r="L198" s="11" t="s">
         <v>5</v>
       </c>
@@ -7384,11 +7391,11 @@
       <c r="C199" s="23"/>
       <c r="D199" s="23"/>
       <c r="E199" s="23"/>
-      <c r="F199" s="27"/>
-      <c r="G199" s="27"/>
-      <c r="H199" s="27"/>
-      <c r="I199" s="28"/>
-      <c r="J199" s="24"/>
+      <c r="F199" s="28"/>
+      <c r="G199" s="28"/>
+      <c r="H199" s="28"/>
+      <c r="I199" s="25"/>
+      <c r="J199" s="29"/>
       <c r="L199" s="12" t="s">
         <v>15</v>
       </c>
@@ -7417,11 +7424,11 @@
       <c r="C200" s="23"/>
       <c r="D200" s="23"/>
       <c r="E200" s="23"/>
-      <c r="F200" s="27"/>
-      <c r="G200" s="27"/>
-      <c r="H200" s="27"/>
-      <c r="I200" s="28"/>
-      <c r="J200" s="24"/>
+      <c r="F200" s="28"/>
+      <c r="G200" s="28"/>
+      <c r="H200" s="28"/>
+      <c r="I200" s="25"/>
+      <c r="J200" s="29"/>
       <c r="L200" s="14" t="s">
         <v>17</v>
       </c>
@@ -7448,11 +7455,11 @@
       <c r="C201" s="23"/>
       <c r="D201" s="23"/>
       <c r="E201" s="23"/>
-      <c r="F201" s="27"/>
-      <c r="G201" s="27"/>
-      <c r="H201" s="27"/>
-      <c r="I201" s="28"/>
-      <c r="J201" s="24"/>
+      <c r="F201" s="28"/>
+      <c r="G201" s="28"/>
+      <c r="H201" s="28"/>
+      <c r="I201" s="25"/>
+      <c r="J201" s="29"/>
       <c r="L201" s="15" t="s">
         <v>23</v>
       </c>
@@ -7480,14 +7487,14 @@
       </c>
       <c r="D203" s="23"/>
       <c r="E203" s="23"/>
-      <c r="F203" s="29" t="s">
+      <c r="F203" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="23"/>
       <c r="H203" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I203" s="25" t="s">
+      <c r="I203" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J203" s="23"/>
@@ -7519,10 +7526,10 @@
       <c r="C204" s="23"/>
       <c r="D204" s="23"/>
       <c r="E204" s="23"/>
-      <c r="F204" s="29"/>
+      <c r="F204" s="24"/>
       <c r="G204" s="23"/>
       <c r="H204" s="23"/>
-      <c r="I204" s="26"/>
+      <c r="I204" s="27"/>
       <c r="J204" s="23"/>
       <c r="L204" s="11" t="s">
         <v>5</v>
@@ -7562,10 +7569,10 @@
       <c r="C205" s="23"/>
       <c r="D205" s="23"/>
       <c r="E205" s="23"/>
-      <c r="F205" s="29"/>
+      <c r="F205" s="24"/>
       <c r="G205" s="23"/>
       <c r="H205" s="23"/>
-      <c r="I205" s="26"/>
+      <c r="I205" s="27"/>
       <c r="J205" s="23"/>
       <c r="L205" s="12" t="s">
         <v>15</v>
@@ -7587,10 +7594,10 @@
       <c r="C206" s="23"/>
       <c r="D206" s="23"/>
       <c r="E206" s="23"/>
-      <c r="F206" s="29"/>
+      <c r="F206" s="24"/>
       <c r="G206" s="23"/>
       <c r="H206" s="23"/>
-      <c r="I206" s="26"/>
+      <c r="I206" s="27"/>
       <c r="J206" s="23"/>
       <c r="L206" s="14" t="s">
         <v>17</v>
@@ -7618,10 +7625,10 @@
       <c r="C207" s="23"/>
       <c r="D207" s="23"/>
       <c r="E207" s="23"/>
-      <c r="F207" s="29"/>
+      <c r="F207" s="24"/>
       <c r="G207" s="23"/>
       <c r="H207" s="23"/>
-      <c r="I207" s="26"/>
+      <c r="I207" s="27"/>
       <c r="J207" s="23"/>
       <c r="L207" s="15" t="s">
         <v>23</v>
@@ -7650,16 +7657,16 @@
       <c r="F208" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G208" s="29" t="s">
+      <c r="G208" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H208" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I208" s="27" t="s">
+      <c r="I208" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J208" s="28" t="s">
+      <c r="J208" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L208" s="9" t="s">
@@ -7691,10 +7698,10 @@
       <c r="D209" s="23"/>
       <c r="E209" s="23"/>
       <c r="F209" s="23"/>
-      <c r="G209" s="29"/>
+      <c r="G209" s="24"/>
       <c r="H209" s="23"/>
-      <c r="I209" s="27"/>
-      <c r="J209" s="28"/>
+      <c r="I209" s="28"/>
+      <c r="J209" s="25"/>
       <c r="L209" s="11" t="s">
         <v>5</v>
       </c>
@@ -7734,10 +7741,10 @@
       <c r="D210" s="23"/>
       <c r="E210" s="23"/>
       <c r="F210" s="23"/>
-      <c r="G210" s="29"/>
+      <c r="G210" s="24"/>
       <c r="H210" s="23"/>
-      <c r="I210" s="27"/>
-      <c r="J210" s="28"/>
+      <c r="I210" s="28"/>
+      <c r="J210" s="25"/>
       <c r="L210" s="12" t="s">
         <v>15</v>
       </c>
@@ -7767,10 +7774,10 @@
       <c r="D211" s="23"/>
       <c r="E211" s="23"/>
       <c r="F211" s="23"/>
-      <c r="G211" s="29"/>
+      <c r="G211" s="24"/>
       <c r="H211" s="23"/>
-      <c r="I211" s="27"/>
-      <c r="J211" s="28"/>
+      <c r="I211" s="28"/>
+      <c r="J211" s="25"/>
       <c r="L211" s="14" t="s">
         <v>17</v>
       </c>
@@ -7798,10 +7805,10 @@
       <c r="D212" s="23"/>
       <c r="E212" s="23"/>
       <c r="F212" s="23"/>
-      <c r="G212" s="29"/>
+      <c r="G212" s="24"/>
       <c r="H212" s="23"/>
-      <c r="I212" s="27"/>
-      <c r="J212" s="28"/>
+      <c r="I212" s="28"/>
+      <c r="J212" s="25"/>
       <c r="L212" s="15" t="s">
         <v>23</v>
       </c>
@@ -7826,19 +7833,19 @@
       </c>
       <c r="D213" s="23"/>
       <c r="E213" s="23"/>
-      <c r="F213" s="27" t="s">
+      <c r="F213" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G213" s="27" t="s">
+      <c r="G213" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H213" s="27" t="s">
+      <c r="H213" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I213" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J213" s="24" t="s">
+      <c r="I213" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J213" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L213" s="9" t="s">
@@ -7869,11 +7876,11 @@
       <c r="C214" s="23"/>
       <c r="D214" s="23"/>
       <c r="E214" s="23"/>
-      <c r="F214" s="27"/>
-      <c r="G214" s="27"/>
-      <c r="H214" s="27"/>
-      <c r="I214" s="28"/>
-      <c r="J214" s="24"/>
+      <c r="F214" s="28"/>
+      <c r="G214" s="28"/>
+      <c r="H214" s="28"/>
+      <c r="I214" s="25"/>
+      <c r="J214" s="29"/>
       <c r="L214" s="11" t="s">
         <v>5</v>
       </c>
@@ -7912,11 +7919,11 @@
       <c r="C215" s="23"/>
       <c r="D215" s="23"/>
       <c r="E215" s="23"/>
-      <c r="F215" s="27"/>
-      <c r="G215" s="27"/>
-      <c r="H215" s="27"/>
-      <c r="I215" s="28"/>
-      <c r="J215" s="24"/>
+      <c r="F215" s="28"/>
+      <c r="G215" s="28"/>
+      <c r="H215" s="28"/>
+      <c r="I215" s="25"/>
+      <c r="J215" s="29"/>
       <c r="L215" s="12" t="s">
         <v>15</v>
       </c>
@@ -7945,11 +7952,11 @@
       <c r="C216" s="23"/>
       <c r="D216" s="23"/>
       <c r="E216" s="23"/>
-      <c r="F216" s="27"/>
-      <c r="G216" s="27"/>
-      <c r="H216" s="27"/>
-      <c r="I216" s="28"/>
-      <c r="J216" s="24"/>
+      <c r="F216" s="28"/>
+      <c r="G216" s="28"/>
+      <c r="H216" s="28"/>
+      <c r="I216" s="25"/>
+      <c r="J216" s="29"/>
       <c r="L216" s="14" t="s">
         <v>17</v>
       </c>
@@ -7976,11 +7983,11 @@
       <c r="C217" s="23"/>
       <c r="D217" s="23"/>
       <c r="E217" s="23"/>
-      <c r="F217" s="27"/>
-      <c r="G217" s="27"/>
-      <c r="H217" s="27"/>
-      <c r="I217" s="28"/>
-      <c r="J217" s="24"/>
+      <c r="F217" s="28"/>
+      <c r="G217" s="28"/>
+      <c r="H217" s="28"/>
+      <c r="I217" s="25"/>
+      <c r="J217" s="29"/>
       <c r="L217" s="15" t="s">
         <v>23</v>
       </c>
@@ -8018,10 +8025,10 @@
       <c r="G220" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H220" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I220" s="25" t="s">
+      <c r="H220" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I220" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J220" s="23"/>
@@ -8055,8 +8062,8 @@
       <c r="E221" s="23"/>
       <c r="F221" s="23"/>
       <c r="G221" s="23"/>
-      <c r="H221" s="29"/>
-      <c r="I221" s="26"/>
+      <c r="H221" s="24"/>
+      <c r="I221" s="27"/>
       <c r="J221" s="23"/>
       <c r="L221" s="11" t="s">
         <v>5</v>
@@ -8098,8 +8105,8 @@
       <c r="E222" s="23"/>
       <c r="F222" s="23"/>
       <c r="G222" s="23"/>
-      <c r="H222" s="29"/>
-      <c r="I222" s="26"/>
+      <c r="H222" s="24"/>
+      <c r="I222" s="27"/>
       <c r="J222" s="23"/>
       <c r="L222" s="12" t="s">
         <v>15</v>
@@ -8123,8 +8130,8 @@
       <c r="E223" s="23"/>
       <c r="F223" s="23"/>
       <c r="G223" s="23"/>
-      <c r="H223" s="29"/>
-      <c r="I223" s="26"/>
+      <c r="H223" s="24"/>
+      <c r="I223" s="27"/>
       <c r="J223" s="23"/>
       <c r="L223" s="14" t="s">
         <v>17</v>
@@ -8154,8 +8161,8 @@
       <c r="E224" s="23"/>
       <c r="F224" s="23"/>
       <c r="G224" s="23"/>
-      <c r="H224" s="29"/>
-      <c r="I224" s="26"/>
+      <c r="H224" s="24"/>
+      <c r="I224" s="27"/>
       <c r="J224" s="23"/>
       <c r="L224" s="15" t="s">
         <v>23</v>
@@ -8181,7 +8188,7 @@
       </c>
       <c r="D225" s="23"/>
       <c r="E225" s="23"/>
-      <c r="F225" s="29" t="s">
+      <c r="F225" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="23" t="s">
@@ -8190,10 +8197,10 @@
       <c r="H225" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I225" s="27" t="s">
+      <c r="I225" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J225" s="28" t="s">
+      <c r="J225" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L225" s="9" t="s">
@@ -8224,11 +8231,11 @@
       <c r="C226" s="23"/>
       <c r="D226" s="23"/>
       <c r="E226" s="23"/>
-      <c r="F226" s="29"/>
+      <c r="F226" s="24"/>
       <c r="G226" s="23"/>
       <c r="H226" s="23"/>
-      <c r="I226" s="27"/>
-      <c r="J226" s="28"/>
+      <c r="I226" s="28"/>
+      <c r="J226" s="25"/>
       <c r="L226" s="11" t="s">
         <v>5</v>
       </c>
@@ -8267,11 +8274,11 @@
       <c r="C227" s="23"/>
       <c r="D227" s="23"/>
       <c r="E227" s="23"/>
-      <c r="F227" s="29"/>
+      <c r="F227" s="24"/>
       <c r="G227" s="23"/>
       <c r="H227" s="23"/>
-      <c r="I227" s="27"/>
-      <c r="J227" s="28"/>
+      <c r="I227" s="28"/>
+      <c r="J227" s="25"/>
       <c r="L227" s="12" t="s">
         <v>15</v>
       </c>
@@ -8300,11 +8307,11 @@
       <c r="C228" s="23"/>
       <c r="D228" s="23"/>
       <c r="E228" s="23"/>
-      <c r="F228" s="29"/>
+      <c r="F228" s="24"/>
       <c r="G228" s="23"/>
       <c r="H228" s="23"/>
-      <c r="I228" s="27"/>
-      <c r="J228" s="28"/>
+      <c r="I228" s="28"/>
+      <c r="J228" s="25"/>
       <c r="L228" s="14" t="s">
         <v>17</v>
       </c>
@@ -8331,11 +8338,11 @@
       <c r="C229" s="23"/>
       <c r="D229" s="23"/>
       <c r="E229" s="23"/>
-      <c r="F229" s="29"/>
+      <c r="F229" s="24"/>
       <c r="G229" s="23"/>
       <c r="H229" s="23"/>
-      <c r="I229" s="27"/>
-      <c r="J229" s="28"/>
+      <c r="I229" s="28"/>
+      <c r="J229" s="25"/>
       <c r="L229" s="15" t="s">
         <v>23</v>
       </c>
@@ -8360,19 +8367,19 @@
       </c>
       <c r="D230" s="23"/>
       <c r="E230" s="23"/>
-      <c r="F230" s="27" t="s">
+      <c r="F230" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G230" s="27" t="s">
+      <c r="G230" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H230" s="27" t="s">
+      <c r="H230" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I230" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J230" s="24" t="s">
+      <c r="I230" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J230" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L230" s="9" t="s">
@@ -8403,11 +8410,11 @@
       <c r="C231" s="23"/>
       <c r="D231" s="23"/>
       <c r="E231" s="23"/>
-      <c r="F231" s="27"/>
-      <c r="G231" s="27"/>
-      <c r="H231" s="27"/>
-      <c r="I231" s="28"/>
-      <c r="J231" s="24"/>
+      <c r="F231" s="28"/>
+      <c r="G231" s="28"/>
+      <c r="H231" s="28"/>
+      <c r="I231" s="25"/>
+      <c r="J231" s="29"/>
       <c r="L231" s="11" t="s">
         <v>5</v>
       </c>
@@ -8446,11 +8453,11 @@
       <c r="C232" s="23"/>
       <c r="D232" s="23"/>
       <c r="E232" s="23"/>
-      <c r="F232" s="27"/>
-      <c r="G232" s="27"/>
-      <c r="H232" s="27"/>
-      <c r="I232" s="28"/>
-      <c r="J232" s="24"/>
+      <c r="F232" s="28"/>
+      <c r="G232" s="28"/>
+      <c r="H232" s="28"/>
+      <c r="I232" s="25"/>
+      <c r="J232" s="29"/>
       <c r="L232" s="12" t="s">
         <v>15</v>
       </c>
@@ -8479,11 +8486,11 @@
       <c r="C233" s="23"/>
       <c r="D233" s="23"/>
       <c r="E233" s="23"/>
-      <c r="F233" s="27"/>
-      <c r="G233" s="27"/>
-      <c r="H233" s="27"/>
-      <c r="I233" s="28"/>
-      <c r="J233" s="24"/>
+      <c r="F233" s="28"/>
+      <c r="G233" s="28"/>
+      <c r="H233" s="28"/>
+      <c r="I233" s="25"/>
+      <c r="J233" s="29"/>
       <c r="L233" s="14" t="s">
         <v>17</v>
       </c>
@@ -8510,11 +8517,11 @@
       <c r="C234" s="23"/>
       <c r="D234" s="23"/>
       <c r="E234" s="23"/>
-      <c r="F234" s="27"/>
-      <c r="G234" s="27"/>
-      <c r="H234" s="27"/>
-      <c r="I234" s="28"/>
-      <c r="J234" s="24"/>
+      <c r="F234" s="28"/>
+      <c r="G234" s="28"/>
+      <c r="H234" s="28"/>
+      <c r="I234" s="25"/>
+      <c r="J234" s="29"/>
       <c r="L234" s="15" t="s">
         <v>23</v>
       </c>
@@ -8545,11 +8552,11 @@
       <c r="F236" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G236" s="29" t="s">
+      <c r="G236" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H236" s="23"/>
-      <c r="I236" s="25" t="s">
+      <c r="I236" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J236" s="23"/>
@@ -8582,9 +8589,9 @@
       <c r="D237" s="23"/>
       <c r="E237" s="23"/>
       <c r="F237" s="23"/>
-      <c r="G237" s="29"/>
+      <c r="G237" s="24"/>
       <c r="H237" s="23"/>
-      <c r="I237" s="26"/>
+      <c r="I237" s="27"/>
       <c r="J237" s="23"/>
       <c r="L237" s="11" t="s">
         <v>5</v>
@@ -8625,9 +8632,9 @@
       <c r="D238" s="23"/>
       <c r="E238" s="23"/>
       <c r="F238" s="23"/>
-      <c r="G238" s="29"/>
+      <c r="G238" s="24"/>
       <c r="H238" s="23"/>
-      <c r="I238" s="26"/>
+      <c r="I238" s="27"/>
       <c r="J238" s="23"/>
       <c r="L238" s="12" t="s">
         <v>15</v>
@@ -8650,9 +8657,9 @@
       <c r="D239" s="23"/>
       <c r="E239" s="23"/>
       <c r="F239" s="23"/>
-      <c r="G239" s="29"/>
+      <c r="G239" s="24"/>
       <c r="H239" s="23"/>
-      <c r="I239" s="26"/>
+      <c r="I239" s="27"/>
       <c r="J239" s="23"/>
       <c r="L239" s="14" t="s">
         <v>17</v>
@@ -8681,9 +8688,9 @@
       <c r="D240" s="23"/>
       <c r="E240" s="23"/>
       <c r="F240" s="23"/>
-      <c r="G240" s="29"/>
+      <c r="G240" s="24"/>
       <c r="H240" s="23"/>
-      <c r="I240" s="26"/>
+      <c r="I240" s="27"/>
       <c r="J240" s="23"/>
       <c r="L240" s="15" t="s">
         <v>23</v>
@@ -8715,13 +8722,13 @@
       <c r="G241" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H241" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I241" s="27" t="s">
+      <c r="H241" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I241" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J241" s="28" t="s">
+      <c r="J241" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L241" s="9" t="s">
@@ -8754,9 +8761,9 @@
       <c r="E242" s="23"/>
       <c r="F242" s="23"/>
       <c r="G242" s="23"/>
-      <c r="H242" s="29"/>
-      <c r="I242" s="27"/>
-      <c r="J242" s="28"/>
+      <c r="H242" s="24"/>
+      <c r="I242" s="28"/>
+      <c r="J242" s="25"/>
       <c r="L242" s="11" t="s">
         <v>5</v>
       </c>
@@ -8797,9 +8804,9 @@
       <c r="E243" s="23"/>
       <c r="F243" s="23"/>
       <c r="G243" s="23"/>
-      <c r="H243" s="29"/>
-      <c r="I243" s="27"/>
-      <c r="J243" s="28"/>
+      <c r="H243" s="24"/>
+      <c r="I243" s="28"/>
+      <c r="J243" s="25"/>
       <c r="L243" s="12" t="s">
         <v>15</v>
       </c>
@@ -8830,9 +8837,9 @@
       <c r="E244" s="23"/>
       <c r="F244" s="23"/>
       <c r="G244" s="23"/>
-      <c r="H244" s="29"/>
-      <c r="I244" s="27"/>
-      <c r="J244" s="28"/>
+      <c r="H244" s="24"/>
+      <c r="I244" s="28"/>
+      <c r="J244" s="25"/>
       <c r="L244" s="14" t="s">
         <v>17</v>
       </c>
@@ -8861,9 +8868,9 @@
       <c r="E245" s="23"/>
       <c r="F245" s="23"/>
       <c r="G245" s="23"/>
-      <c r="H245" s="29"/>
-      <c r="I245" s="27"/>
-      <c r="J245" s="28"/>
+      <c r="H245" s="24"/>
+      <c r="I245" s="28"/>
+      <c r="J245" s="25"/>
       <c r="L245" s="15" t="s">
         <v>23</v>
       </c>
@@ -8888,19 +8895,19 @@
       </c>
       <c r="D246" s="23"/>
       <c r="E246" s="23"/>
-      <c r="F246" s="27" t="s">
+      <c r="F246" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G246" s="27" t="s">
+      <c r="G246" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H246" s="27" t="s">
+      <c r="H246" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I246" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J246" s="24" t="s">
+      <c r="I246" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J246" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L246" s="9" t="s">
@@ -8931,11 +8938,11 @@
       <c r="C247" s="23"/>
       <c r="D247" s="23"/>
       <c r="E247" s="23"/>
-      <c r="F247" s="27"/>
-      <c r="G247" s="27"/>
-      <c r="H247" s="27"/>
-      <c r="I247" s="28"/>
-      <c r="J247" s="24"/>
+      <c r="F247" s="28"/>
+      <c r="G247" s="28"/>
+      <c r="H247" s="28"/>
+      <c r="I247" s="25"/>
+      <c r="J247" s="29"/>
       <c r="L247" s="11" t="s">
         <v>5</v>
       </c>
@@ -8974,11 +8981,11 @@
       <c r="C248" s="23"/>
       <c r="D248" s="23"/>
       <c r="E248" s="23"/>
-      <c r="F248" s="27"/>
-      <c r="G248" s="27"/>
-      <c r="H248" s="27"/>
-      <c r="I248" s="28"/>
-      <c r="J248" s="24"/>
+      <c r="F248" s="28"/>
+      <c r="G248" s="28"/>
+      <c r="H248" s="28"/>
+      <c r="I248" s="25"/>
+      <c r="J248" s="29"/>
       <c r="L248" s="12" t="s">
         <v>15</v>
       </c>
@@ -9007,11 +9014,11 @@
       <c r="C249" s="23"/>
       <c r="D249" s="23"/>
       <c r="E249" s="23"/>
-      <c r="F249" s="27"/>
-      <c r="G249" s="27"/>
-      <c r="H249" s="27"/>
-      <c r="I249" s="28"/>
-      <c r="J249" s="24"/>
+      <c r="F249" s="28"/>
+      <c r="G249" s="28"/>
+      <c r="H249" s="28"/>
+      <c r="I249" s="25"/>
+      <c r="J249" s="29"/>
       <c r="L249" s="14" t="s">
         <v>17</v>
       </c>
@@ -9038,11 +9045,11 @@
       <c r="C250" s="23"/>
       <c r="D250" s="23"/>
       <c r="E250" s="23"/>
-      <c r="F250" s="27"/>
-      <c r="G250" s="27"/>
-      <c r="H250" s="27"/>
-      <c r="I250" s="28"/>
-      <c r="J250" s="24"/>
+      <c r="F250" s="28"/>
+      <c r="G250" s="28"/>
+      <c r="H250" s="28"/>
+      <c r="I250" s="25"/>
+      <c r="J250" s="29"/>
       <c r="L250" s="15" t="s">
         <v>23</v>
       </c>
@@ -9070,14 +9077,14 @@
       </c>
       <c r="D252" s="23"/>
       <c r="E252" s="23"/>
-      <c r="F252" s="29" t="s">
+      <c r="F252" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G252" s="23"/>
       <c r="H252" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I252" s="25" t="s">
+      <c r="I252" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J252" s="23"/>
@@ -9109,10 +9116,10 @@
       <c r="C253" s="23"/>
       <c r="D253" s="23"/>
       <c r="E253" s="23"/>
-      <c r="F253" s="29"/>
+      <c r="F253" s="24"/>
       <c r="G253" s="23"/>
       <c r="H253" s="23"/>
-      <c r="I253" s="26"/>
+      <c r="I253" s="27"/>
       <c r="J253" s="23"/>
       <c r="L253" s="11" t="s">
         <v>5</v>
@@ -9152,10 +9159,10 @@
       <c r="C254" s="23"/>
       <c r="D254" s="23"/>
       <c r="E254" s="23"/>
-      <c r="F254" s="29"/>
+      <c r="F254" s="24"/>
       <c r="G254" s="23"/>
       <c r="H254" s="23"/>
-      <c r="I254" s="26"/>
+      <c r="I254" s="27"/>
       <c r="J254" s="23"/>
       <c r="L254" s="12" t="s">
         <v>15</v>
@@ -9177,10 +9184,10 @@
       <c r="C255" s="23"/>
       <c r="D255" s="23"/>
       <c r="E255" s="23"/>
-      <c r="F255" s="29"/>
+      <c r="F255" s="24"/>
       <c r="G255" s="23"/>
       <c r="H255" s="23"/>
-      <c r="I255" s="26"/>
+      <c r="I255" s="27"/>
       <c r="J255" s="23"/>
       <c r="L255" s="14" t="s">
         <v>17</v>
@@ -9208,10 +9215,10 @@
       <c r="C256" s="23"/>
       <c r="D256" s="23"/>
       <c r="E256" s="23"/>
-      <c r="F256" s="29"/>
+      <c r="F256" s="24"/>
       <c r="G256" s="23"/>
       <c r="H256" s="23"/>
-      <c r="I256" s="26"/>
+      <c r="I256" s="27"/>
       <c r="J256" s="23"/>
       <c r="L256" s="15" t="s">
         <v>23</v>
@@ -9240,16 +9247,16 @@
       <c r="F257" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G257" s="29" t="s">
+      <c r="G257" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H257" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I257" s="27" t="s">
+      <c r="I257" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J257" s="28" t="s">
+      <c r="J257" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L257" s="9" t="s">
@@ -9281,10 +9288,10 @@
       <c r="D258" s="23"/>
       <c r="E258" s="23"/>
       <c r="F258" s="23"/>
-      <c r="G258" s="29"/>
+      <c r="G258" s="24"/>
       <c r="H258" s="23"/>
-      <c r="I258" s="27"/>
-      <c r="J258" s="28"/>
+      <c r="I258" s="28"/>
+      <c r="J258" s="25"/>
       <c r="L258" s="11" t="s">
         <v>5</v>
       </c>
@@ -9324,10 +9331,10 @@
       <c r="D259" s="23"/>
       <c r="E259" s="23"/>
       <c r="F259" s="23"/>
-      <c r="G259" s="29"/>
+      <c r="G259" s="24"/>
       <c r="H259" s="23"/>
-      <c r="I259" s="27"/>
-      <c r="J259" s="28"/>
+      <c r="I259" s="28"/>
+      <c r="J259" s="25"/>
       <c r="L259" s="12" t="s">
         <v>15</v>
       </c>
@@ -9357,10 +9364,10 @@
       <c r="D260" s="23"/>
       <c r="E260" s="23"/>
       <c r="F260" s="23"/>
-      <c r="G260" s="29"/>
+      <c r="G260" s="24"/>
       <c r="H260" s="23"/>
-      <c r="I260" s="27"/>
-      <c r="J260" s="28"/>
+      <c r="I260" s="28"/>
+      <c r="J260" s="25"/>
       <c r="L260" s="14" t="s">
         <v>17</v>
       </c>
@@ -9388,10 +9395,10 @@
       <c r="D261" s="23"/>
       <c r="E261" s="23"/>
       <c r="F261" s="23"/>
-      <c r="G261" s="29"/>
+      <c r="G261" s="24"/>
       <c r="H261" s="23"/>
-      <c r="I261" s="27"/>
-      <c r="J261" s="28"/>
+      <c r="I261" s="28"/>
+      <c r="J261" s="25"/>
       <c r="L261" s="15" t="s">
         <v>23</v>
       </c>
@@ -9416,19 +9423,19 @@
       </c>
       <c r="D262" s="23"/>
       <c r="E262" s="23"/>
-      <c r="F262" s="27" t="s">
+      <c r="F262" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G262" s="27" t="s">
+      <c r="G262" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H262" s="27" t="s">
+      <c r="H262" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I262" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J262" s="24" t="s">
+      <c r="I262" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J262" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L262" s="9" t="s">
@@ -9459,11 +9466,11 @@
       <c r="C263" s="23"/>
       <c r="D263" s="23"/>
       <c r="E263" s="23"/>
-      <c r="F263" s="27"/>
-      <c r="G263" s="27"/>
-      <c r="H263" s="27"/>
-      <c r="I263" s="28"/>
-      <c r="J263" s="24"/>
+      <c r="F263" s="28"/>
+      <c r="G263" s="28"/>
+      <c r="H263" s="28"/>
+      <c r="I263" s="25"/>
+      <c r="J263" s="29"/>
       <c r="L263" s="11" t="s">
         <v>5</v>
       </c>
@@ -9502,11 +9509,11 @@
       <c r="C264" s="23"/>
       <c r="D264" s="23"/>
       <c r="E264" s="23"/>
-      <c r="F264" s="27"/>
-      <c r="G264" s="27"/>
-      <c r="H264" s="27"/>
-      <c r="I264" s="28"/>
-      <c r="J264" s="24"/>
+      <c r="F264" s="28"/>
+      <c r="G264" s="28"/>
+      <c r="H264" s="28"/>
+      <c r="I264" s="25"/>
+      <c r="J264" s="29"/>
       <c r="L264" s="12" t="s">
         <v>15</v>
       </c>
@@ -9535,11 +9542,11 @@
       <c r="C265" s="23"/>
       <c r="D265" s="23"/>
       <c r="E265" s="23"/>
-      <c r="F265" s="27"/>
-      <c r="G265" s="27"/>
-      <c r="H265" s="27"/>
-      <c r="I265" s="28"/>
-      <c r="J265" s="24"/>
+      <c r="F265" s="28"/>
+      <c r="G265" s="28"/>
+      <c r="H265" s="28"/>
+      <c r="I265" s="25"/>
+      <c r="J265" s="29"/>
       <c r="L265" s="14" t="s">
         <v>17</v>
       </c>
@@ -9566,11 +9573,11 @@
       <c r="C266" s="23"/>
       <c r="D266" s="23"/>
       <c r="E266" s="23"/>
-      <c r="F266" s="27"/>
-      <c r="G266" s="27"/>
-      <c r="H266" s="27"/>
-      <c r="I266" s="28"/>
-      <c r="J266" s="24"/>
+      <c r="F266" s="28"/>
+      <c r="G266" s="28"/>
+      <c r="H266" s="28"/>
+      <c r="I266" s="25"/>
+      <c r="J266" s="29"/>
       <c r="L266" s="15" t="s">
         <v>23</v>
       </c>
@@ -9601,7 +9608,7 @@
       <c r="F269" s="23"/>
       <c r="G269" s="23"/>
       <c r="H269" s="23"/>
-      <c r="I269" s="25" t="s">
+      <c r="I269" s="26" t="s">
         <v>45</v>
       </c>
       <c r="J269" s="23"/>
@@ -9633,7 +9640,7 @@
       <c r="F270" s="23"/>
       <c r="G270" s="23"/>
       <c r="H270" s="23"/>
-      <c r="I270" s="26"/>
+      <c r="I270" s="27"/>
       <c r="J270" s="23"/>
       <c r="L270" s="11" t="s">
         <v>5</v>
@@ -9676,7 +9683,7 @@
       <c r="F271" s="23"/>
       <c r="G271" s="23"/>
       <c r="H271" s="23"/>
-      <c r="I271" s="26"/>
+      <c r="I271" s="27"/>
       <c r="J271" s="23"/>
       <c r="L271" s="12" t="s">
         <v>15</v>
@@ -9701,7 +9708,7 @@
       <c r="F272" s="23"/>
       <c r="G272" s="23"/>
       <c r="H272" s="23"/>
-      <c r="I272" s="26"/>
+      <c r="I272" s="27"/>
       <c r="J272" s="23"/>
       <c r="L272" s="14" t="s">
         <v>17</v>
@@ -9731,7 +9738,7 @@
       <c r="F273" s="23"/>
       <c r="G273" s="23"/>
       <c r="H273" s="23"/>
-      <c r="I273" s="26"/>
+      <c r="I273" s="27"/>
       <c r="J273" s="23"/>
       <c r="L273" s="15" t="s">
         <v>23</v>
@@ -9757,10 +9764,10 @@
       <c r="F274" s="23"/>
       <c r="G274" s="23"/>
       <c r="H274" s="23"/>
-      <c r="I274" s="27" t="s">
+      <c r="I274" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J274" s="28" t="s">
+      <c r="J274" s="25" t="s">
         <v>26</v>
       </c>
       <c r="L274" s="9" t="s">
@@ -9791,8 +9798,8 @@
       <c r="F275" s="23"/>
       <c r="G275" s="23"/>
       <c r="H275" s="23"/>
-      <c r="I275" s="27"/>
-      <c r="J275" s="28"/>
+      <c r="I275" s="28"/>
+      <c r="J275" s="25"/>
       <c r="L275" s="11" t="s">
         <v>5</v>
       </c>
@@ -9834,8 +9841,8 @@
       <c r="F276" s="23"/>
       <c r="G276" s="23"/>
       <c r="H276" s="23"/>
-      <c r="I276" s="27"/>
-      <c r="J276" s="28"/>
+      <c r="I276" s="28"/>
+      <c r="J276" s="25"/>
       <c r="L276" s="12" t="s">
         <v>15</v>
       </c>
@@ -9867,8 +9874,8 @@
       <c r="F277" s="23"/>
       <c r="G277" s="23"/>
       <c r="H277" s="23"/>
-      <c r="I277" s="27"/>
-      <c r="J277" s="28"/>
+      <c r="I277" s="28"/>
+      <c r="J277" s="25"/>
       <c r="L277" s="14" t="s">
         <v>17</v>
       </c>
@@ -9897,8 +9904,8 @@
       <c r="F278" s="23"/>
       <c r="G278" s="23"/>
       <c r="H278" s="23"/>
-      <c r="I278" s="27"/>
-      <c r="J278" s="28"/>
+      <c r="I278" s="28"/>
+      <c r="J278" s="25"/>
       <c r="L278" s="15" t="s">
         <v>23</v>
       </c>
@@ -9927,7 +9934,7 @@
       <c r="G279" s="23"/>
       <c r="H279" s="23"/>
       <c r="I279" s="23"/>
-      <c r="J279" s="24" t="s">
+      <c r="J279" s="29" t="s">
         <v>34</v>
       </c>
       <c r="L279" s="9" t="s">
@@ -9962,7 +9969,7 @@
       <c r="G280" s="23"/>
       <c r="H280" s="23"/>
       <c r="I280" s="23"/>
-      <c r="J280" s="24"/>
+      <c r="J280" s="29"/>
       <c r="L280" s="11" t="s">
         <v>5</v>
       </c>
@@ -10005,7 +10012,7 @@
       <c r="G281" s="23"/>
       <c r="H281" s="23"/>
       <c r="I281" s="23"/>
-      <c r="J281" s="24"/>
+      <c r="J281" s="29"/>
       <c r="L281" s="12" t="s">
         <v>15</v>
       </c>
@@ -10030,7 +10037,7 @@
       <c r="G282" s="23"/>
       <c r="H282" s="23"/>
       <c r="I282" s="23"/>
-      <c r="J282" s="24"/>
+      <c r="J282" s="29"/>
       <c r="L282" s="14" t="s">
         <v>17</v>
       </c>
@@ -10061,7 +10068,7 @@
       <c r="G283" s="23"/>
       <c r="H283" s="23"/>
       <c r="I283" s="23"/>
-      <c r="J283" s="24"/>
+      <c r="J283" s="29"/>
       <c r="L283" s="15" t="s">
         <v>23</v>
       </c>
@@ -10082,390 +10089,6 @@
     </row>
   </sheetData>
   <mergeCells count="408">
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="F24:F28"/>
-    <mergeCell ref="G24:G28"/>
-    <mergeCell ref="H24:H28"/>
-    <mergeCell ref="I24:I28"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I40:I44"/>
-    <mergeCell ref="J40:J44"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="E45:E49"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="I45:I49"/>
-    <mergeCell ref="J45:J49"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="E40:E44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="H40:H44"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="D56:D60"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="F56:F60"/>
-    <mergeCell ref="G56:G60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="I56:I60"/>
-    <mergeCell ref="J56:J60"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F66:F70"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="I66:I70"/>
-    <mergeCell ref="J66:J70"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="I73:I77"/>
-    <mergeCell ref="J73:J77"/>
-    <mergeCell ref="C78:C82"/>
-    <mergeCell ref="D78:D82"/>
-    <mergeCell ref="E78:E82"/>
-    <mergeCell ref="F78:F82"/>
-    <mergeCell ref="G78:G82"/>
-    <mergeCell ref="H78:H82"/>
-    <mergeCell ref="I78:I82"/>
-    <mergeCell ref="J78:J82"/>
-    <mergeCell ref="C73:C77"/>
-    <mergeCell ref="D73:D77"/>
-    <mergeCell ref="E73:E77"/>
-    <mergeCell ref="F73:F77"/>
-    <mergeCell ref="G73:G77"/>
-    <mergeCell ref="H73:H77"/>
-    <mergeCell ref="I83:I87"/>
-    <mergeCell ref="J83:J87"/>
-    <mergeCell ref="C89:C93"/>
-    <mergeCell ref="D89:D93"/>
-    <mergeCell ref="E89:E93"/>
-    <mergeCell ref="F89:F93"/>
-    <mergeCell ref="G89:G93"/>
-    <mergeCell ref="H89:H93"/>
-    <mergeCell ref="I89:I93"/>
-    <mergeCell ref="J89:J93"/>
-    <mergeCell ref="C83:C87"/>
-    <mergeCell ref="D83:D87"/>
-    <mergeCell ref="E83:E87"/>
-    <mergeCell ref="F83:F87"/>
-    <mergeCell ref="G83:G87"/>
-    <mergeCell ref="H83:H87"/>
-    <mergeCell ref="I94:I98"/>
-    <mergeCell ref="J94:J98"/>
-    <mergeCell ref="C99:C103"/>
-    <mergeCell ref="D99:D103"/>
-    <mergeCell ref="E99:E103"/>
-    <mergeCell ref="F99:F103"/>
-    <mergeCell ref="G99:G103"/>
-    <mergeCell ref="H99:H103"/>
-    <mergeCell ref="I99:I103"/>
-    <mergeCell ref="J99:J103"/>
-    <mergeCell ref="C94:C98"/>
-    <mergeCell ref="D94:D98"/>
-    <mergeCell ref="E94:E98"/>
-    <mergeCell ref="F94:F98"/>
-    <mergeCell ref="G94:G98"/>
-    <mergeCell ref="H94:H98"/>
-    <mergeCell ref="I105:I109"/>
-    <mergeCell ref="J105:J109"/>
-    <mergeCell ref="C110:C114"/>
-    <mergeCell ref="D110:D114"/>
-    <mergeCell ref="E110:E114"/>
-    <mergeCell ref="F110:F114"/>
-    <mergeCell ref="G110:G114"/>
-    <mergeCell ref="H110:H114"/>
-    <mergeCell ref="I110:I114"/>
-    <mergeCell ref="J110:J114"/>
-    <mergeCell ref="C105:C109"/>
-    <mergeCell ref="D105:D109"/>
-    <mergeCell ref="E105:E109"/>
-    <mergeCell ref="F105:F109"/>
-    <mergeCell ref="G105:G109"/>
-    <mergeCell ref="H105:H109"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="J115:J119"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="G122:G126"/>
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="C115:C119"/>
-    <mergeCell ref="D115:D119"/>
-    <mergeCell ref="E115:E119"/>
-    <mergeCell ref="F115:F119"/>
-    <mergeCell ref="G115:G119"/>
-    <mergeCell ref="H115:H119"/>
-    <mergeCell ref="I127:I131"/>
-    <mergeCell ref="J127:J131"/>
-    <mergeCell ref="C132:C136"/>
-    <mergeCell ref="D132:D136"/>
-    <mergeCell ref="E132:E136"/>
-    <mergeCell ref="F132:F136"/>
-    <mergeCell ref="G132:G136"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="I132:I136"/>
-    <mergeCell ref="J132:J136"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="D127:D131"/>
-    <mergeCell ref="E127:E131"/>
-    <mergeCell ref="F127:F131"/>
-    <mergeCell ref="G127:G131"/>
-    <mergeCell ref="H127:H131"/>
-    <mergeCell ref="I138:I142"/>
-    <mergeCell ref="J138:J142"/>
-    <mergeCell ref="C143:C147"/>
-    <mergeCell ref="D143:D147"/>
-    <mergeCell ref="E143:E147"/>
-    <mergeCell ref="F143:F147"/>
-    <mergeCell ref="G143:G147"/>
-    <mergeCell ref="H143:H147"/>
-    <mergeCell ref="I143:I147"/>
-    <mergeCell ref="J143:J147"/>
-    <mergeCell ref="C138:C142"/>
-    <mergeCell ref="D138:D142"/>
-    <mergeCell ref="E138:E142"/>
-    <mergeCell ref="F138:F142"/>
-    <mergeCell ref="G138:G142"/>
-    <mergeCell ref="H138:H142"/>
-    <mergeCell ref="I148:I152"/>
-    <mergeCell ref="J148:J152"/>
-    <mergeCell ref="C154:C158"/>
-    <mergeCell ref="D154:D158"/>
-    <mergeCell ref="E154:E158"/>
-    <mergeCell ref="F154:F158"/>
-    <mergeCell ref="G154:G158"/>
-    <mergeCell ref="H154:H158"/>
-    <mergeCell ref="I154:I158"/>
-    <mergeCell ref="J154:J158"/>
-    <mergeCell ref="C148:C152"/>
-    <mergeCell ref="D148:D152"/>
-    <mergeCell ref="E148:E152"/>
-    <mergeCell ref="F148:F152"/>
-    <mergeCell ref="G148:G152"/>
-    <mergeCell ref="H148:H152"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="J159:J163"/>
-    <mergeCell ref="C164:C168"/>
-    <mergeCell ref="D164:D168"/>
-    <mergeCell ref="E164:E168"/>
-    <mergeCell ref="F164:F168"/>
-    <mergeCell ref="G164:G168"/>
-    <mergeCell ref="H164:H168"/>
-    <mergeCell ref="I164:I168"/>
-    <mergeCell ref="J164:J168"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="H159:H163"/>
-    <mergeCell ref="I171:I175"/>
-    <mergeCell ref="J171:J175"/>
-    <mergeCell ref="C176:C180"/>
-    <mergeCell ref="D176:D180"/>
-    <mergeCell ref="E176:E180"/>
-    <mergeCell ref="F176:F180"/>
-    <mergeCell ref="G176:G180"/>
-    <mergeCell ref="H176:H180"/>
-    <mergeCell ref="I176:I180"/>
-    <mergeCell ref="J176:J180"/>
-    <mergeCell ref="C171:C175"/>
-    <mergeCell ref="D171:D175"/>
-    <mergeCell ref="E171:E175"/>
-    <mergeCell ref="F171:F175"/>
-    <mergeCell ref="G171:G175"/>
-    <mergeCell ref="H171:H175"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="J181:J185"/>
-    <mergeCell ref="C187:C191"/>
-    <mergeCell ref="D187:D191"/>
-    <mergeCell ref="E187:E191"/>
-    <mergeCell ref="F187:F191"/>
-    <mergeCell ref="G187:G191"/>
-    <mergeCell ref="H187:H191"/>
-    <mergeCell ref="I187:I191"/>
-    <mergeCell ref="J187:J191"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="H181:H185"/>
-    <mergeCell ref="I192:I196"/>
-    <mergeCell ref="J192:J196"/>
-    <mergeCell ref="C197:C201"/>
-    <mergeCell ref="D197:D201"/>
-    <mergeCell ref="E197:E201"/>
-    <mergeCell ref="F197:F201"/>
-    <mergeCell ref="G197:G201"/>
-    <mergeCell ref="H197:H201"/>
-    <mergeCell ref="I197:I201"/>
-    <mergeCell ref="J197:J201"/>
-    <mergeCell ref="C192:C196"/>
-    <mergeCell ref="D192:D196"/>
-    <mergeCell ref="E192:E196"/>
-    <mergeCell ref="F192:F196"/>
-    <mergeCell ref="G192:G196"/>
-    <mergeCell ref="H192:H196"/>
-    <mergeCell ref="I203:I207"/>
-    <mergeCell ref="J203:J207"/>
-    <mergeCell ref="C208:C212"/>
-    <mergeCell ref="D208:D212"/>
-    <mergeCell ref="E208:E212"/>
-    <mergeCell ref="F208:F212"/>
-    <mergeCell ref="G208:G212"/>
-    <mergeCell ref="H208:H212"/>
-    <mergeCell ref="I208:I212"/>
-    <mergeCell ref="J208:J212"/>
-    <mergeCell ref="C203:C207"/>
-    <mergeCell ref="D203:D207"/>
-    <mergeCell ref="E203:E207"/>
-    <mergeCell ref="F203:F207"/>
-    <mergeCell ref="G203:G207"/>
-    <mergeCell ref="H203:H207"/>
-    <mergeCell ref="I213:I217"/>
-    <mergeCell ref="J213:J217"/>
-    <mergeCell ref="C220:C224"/>
-    <mergeCell ref="D220:D224"/>
-    <mergeCell ref="E220:E224"/>
-    <mergeCell ref="F220:F224"/>
-    <mergeCell ref="G220:G224"/>
-    <mergeCell ref="H220:H224"/>
-    <mergeCell ref="I220:I224"/>
-    <mergeCell ref="J220:J224"/>
-    <mergeCell ref="C213:C217"/>
-    <mergeCell ref="D213:D217"/>
-    <mergeCell ref="E213:E217"/>
-    <mergeCell ref="F213:F217"/>
-    <mergeCell ref="G213:G217"/>
-    <mergeCell ref="H213:H217"/>
-    <mergeCell ref="I225:I229"/>
-    <mergeCell ref="J225:J229"/>
-    <mergeCell ref="C230:C234"/>
-    <mergeCell ref="D230:D234"/>
-    <mergeCell ref="E230:E234"/>
-    <mergeCell ref="F230:F234"/>
-    <mergeCell ref="G230:G234"/>
-    <mergeCell ref="H230:H234"/>
-    <mergeCell ref="I230:I234"/>
-    <mergeCell ref="J230:J234"/>
-    <mergeCell ref="C225:C229"/>
-    <mergeCell ref="D225:D229"/>
-    <mergeCell ref="E225:E229"/>
-    <mergeCell ref="F225:F229"/>
-    <mergeCell ref="G225:G229"/>
-    <mergeCell ref="H225:H229"/>
-    <mergeCell ref="I236:I240"/>
-    <mergeCell ref="J236:J240"/>
-    <mergeCell ref="C241:C245"/>
-    <mergeCell ref="D241:D245"/>
-    <mergeCell ref="E241:E245"/>
-    <mergeCell ref="F241:F245"/>
-    <mergeCell ref="G241:G245"/>
-    <mergeCell ref="H241:H245"/>
-    <mergeCell ref="I241:I245"/>
-    <mergeCell ref="J241:J245"/>
-    <mergeCell ref="C236:C240"/>
-    <mergeCell ref="D236:D240"/>
-    <mergeCell ref="E236:E240"/>
-    <mergeCell ref="F236:F240"/>
-    <mergeCell ref="G236:G240"/>
-    <mergeCell ref="H236:H240"/>
-    <mergeCell ref="I246:I250"/>
-    <mergeCell ref="J246:J250"/>
-    <mergeCell ref="C252:C256"/>
-    <mergeCell ref="D252:D256"/>
-    <mergeCell ref="E252:E256"/>
-    <mergeCell ref="F252:F256"/>
-    <mergeCell ref="G252:G256"/>
-    <mergeCell ref="H252:H256"/>
-    <mergeCell ref="I252:I256"/>
-    <mergeCell ref="J252:J256"/>
-    <mergeCell ref="C246:C250"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="E246:E250"/>
-    <mergeCell ref="F246:F250"/>
-    <mergeCell ref="G246:G250"/>
-    <mergeCell ref="H246:H250"/>
-    <mergeCell ref="I257:I261"/>
-    <mergeCell ref="J257:J261"/>
-    <mergeCell ref="C262:C266"/>
-    <mergeCell ref="D262:D266"/>
-    <mergeCell ref="E262:E266"/>
-    <mergeCell ref="F262:F266"/>
-    <mergeCell ref="G262:G266"/>
-    <mergeCell ref="H262:H266"/>
-    <mergeCell ref="I262:I266"/>
-    <mergeCell ref="J262:J266"/>
-    <mergeCell ref="C257:C261"/>
-    <mergeCell ref="D257:D261"/>
-    <mergeCell ref="E257:E261"/>
-    <mergeCell ref="F257:F261"/>
-    <mergeCell ref="G257:G261"/>
-    <mergeCell ref="H257:H261"/>
     <mergeCell ref="I279:I283"/>
     <mergeCell ref="J279:J283"/>
     <mergeCell ref="C279:C283"/>
@@ -10490,6 +10113,390 @@
     <mergeCell ref="F269:F273"/>
     <mergeCell ref="G269:G273"/>
     <mergeCell ref="H269:H273"/>
+    <mergeCell ref="I257:I261"/>
+    <mergeCell ref="J257:J261"/>
+    <mergeCell ref="C262:C266"/>
+    <mergeCell ref="D262:D266"/>
+    <mergeCell ref="E262:E266"/>
+    <mergeCell ref="F262:F266"/>
+    <mergeCell ref="G262:G266"/>
+    <mergeCell ref="H262:H266"/>
+    <mergeCell ref="I262:I266"/>
+    <mergeCell ref="J262:J266"/>
+    <mergeCell ref="C257:C261"/>
+    <mergeCell ref="D257:D261"/>
+    <mergeCell ref="E257:E261"/>
+    <mergeCell ref="F257:F261"/>
+    <mergeCell ref="G257:G261"/>
+    <mergeCell ref="H257:H261"/>
+    <mergeCell ref="I246:I250"/>
+    <mergeCell ref="J246:J250"/>
+    <mergeCell ref="C252:C256"/>
+    <mergeCell ref="D252:D256"/>
+    <mergeCell ref="E252:E256"/>
+    <mergeCell ref="F252:F256"/>
+    <mergeCell ref="G252:G256"/>
+    <mergeCell ref="H252:H256"/>
+    <mergeCell ref="I252:I256"/>
+    <mergeCell ref="J252:J256"/>
+    <mergeCell ref="C246:C250"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="E246:E250"/>
+    <mergeCell ref="F246:F250"/>
+    <mergeCell ref="G246:G250"/>
+    <mergeCell ref="H246:H250"/>
+    <mergeCell ref="I236:I240"/>
+    <mergeCell ref="J236:J240"/>
+    <mergeCell ref="C241:C245"/>
+    <mergeCell ref="D241:D245"/>
+    <mergeCell ref="E241:E245"/>
+    <mergeCell ref="F241:F245"/>
+    <mergeCell ref="G241:G245"/>
+    <mergeCell ref="H241:H245"/>
+    <mergeCell ref="I241:I245"/>
+    <mergeCell ref="J241:J245"/>
+    <mergeCell ref="C236:C240"/>
+    <mergeCell ref="D236:D240"/>
+    <mergeCell ref="E236:E240"/>
+    <mergeCell ref="F236:F240"/>
+    <mergeCell ref="G236:G240"/>
+    <mergeCell ref="H236:H240"/>
+    <mergeCell ref="I225:I229"/>
+    <mergeCell ref="J225:J229"/>
+    <mergeCell ref="C230:C234"/>
+    <mergeCell ref="D230:D234"/>
+    <mergeCell ref="E230:E234"/>
+    <mergeCell ref="F230:F234"/>
+    <mergeCell ref="G230:G234"/>
+    <mergeCell ref="H230:H234"/>
+    <mergeCell ref="I230:I234"/>
+    <mergeCell ref="J230:J234"/>
+    <mergeCell ref="C225:C229"/>
+    <mergeCell ref="D225:D229"/>
+    <mergeCell ref="E225:E229"/>
+    <mergeCell ref="F225:F229"/>
+    <mergeCell ref="G225:G229"/>
+    <mergeCell ref="H225:H229"/>
+    <mergeCell ref="I213:I217"/>
+    <mergeCell ref="J213:J217"/>
+    <mergeCell ref="C220:C224"/>
+    <mergeCell ref="D220:D224"/>
+    <mergeCell ref="E220:E224"/>
+    <mergeCell ref="F220:F224"/>
+    <mergeCell ref="G220:G224"/>
+    <mergeCell ref="H220:H224"/>
+    <mergeCell ref="I220:I224"/>
+    <mergeCell ref="J220:J224"/>
+    <mergeCell ref="C213:C217"/>
+    <mergeCell ref="D213:D217"/>
+    <mergeCell ref="E213:E217"/>
+    <mergeCell ref="F213:F217"/>
+    <mergeCell ref="G213:G217"/>
+    <mergeCell ref="H213:H217"/>
+    <mergeCell ref="I203:I207"/>
+    <mergeCell ref="J203:J207"/>
+    <mergeCell ref="C208:C212"/>
+    <mergeCell ref="D208:D212"/>
+    <mergeCell ref="E208:E212"/>
+    <mergeCell ref="F208:F212"/>
+    <mergeCell ref="G208:G212"/>
+    <mergeCell ref="H208:H212"/>
+    <mergeCell ref="I208:I212"/>
+    <mergeCell ref="J208:J212"/>
+    <mergeCell ref="C203:C207"/>
+    <mergeCell ref="D203:D207"/>
+    <mergeCell ref="E203:E207"/>
+    <mergeCell ref="F203:F207"/>
+    <mergeCell ref="G203:G207"/>
+    <mergeCell ref="H203:H207"/>
+    <mergeCell ref="I192:I196"/>
+    <mergeCell ref="J192:J196"/>
+    <mergeCell ref="C197:C201"/>
+    <mergeCell ref="D197:D201"/>
+    <mergeCell ref="E197:E201"/>
+    <mergeCell ref="F197:F201"/>
+    <mergeCell ref="G197:G201"/>
+    <mergeCell ref="H197:H201"/>
+    <mergeCell ref="I197:I201"/>
+    <mergeCell ref="J197:J201"/>
+    <mergeCell ref="C192:C196"/>
+    <mergeCell ref="D192:D196"/>
+    <mergeCell ref="E192:E196"/>
+    <mergeCell ref="F192:F196"/>
+    <mergeCell ref="G192:G196"/>
+    <mergeCell ref="H192:H196"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="J181:J185"/>
+    <mergeCell ref="C187:C191"/>
+    <mergeCell ref="D187:D191"/>
+    <mergeCell ref="E187:E191"/>
+    <mergeCell ref="F187:F191"/>
+    <mergeCell ref="G187:G191"/>
+    <mergeCell ref="H187:H191"/>
+    <mergeCell ref="I187:I191"/>
+    <mergeCell ref="J187:J191"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="H181:H185"/>
+    <mergeCell ref="I171:I175"/>
+    <mergeCell ref="J171:J175"/>
+    <mergeCell ref="C176:C180"/>
+    <mergeCell ref="D176:D180"/>
+    <mergeCell ref="E176:E180"/>
+    <mergeCell ref="F176:F180"/>
+    <mergeCell ref="G176:G180"/>
+    <mergeCell ref="H176:H180"/>
+    <mergeCell ref="I176:I180"/>
+    <mergeCell ref="J176:J180"/>
+    <mergeCell ref="C171:C175"/>
+    <mergeCell ref="D171:D175"/>
+    <mergeCell ref="E171:E175"/>
+    <mergeCell ref="F171:F175"/>
+    <mergeCell ref="G171:G175"/>
+    <mergeCell ref="H171:H175"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="J159:J163"/>
+    <mergeCell ref="C164:C168"/>
+    <mergeCell ref="D164:D168"/>
+    <mergeCell ref="E164:E168"/>
+    <mergeCell ref="F164:F168"/>
+    <mergeCell ref="G164:G168"/>
+    <mergeCell ref="H164:H168"/>
+    <mergeCell ref="I164:I168"/>
+    <mergeCell ref="J164:J168"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="H159:H163"/>
+    <mergeCell ref="I148:I152"/>
+    <mergeCell ref="J148:J152"/>
+    <mergeCell ref="C154:C158"/>
+    <mergeCell ref="D154:D158"/>
+    <mergeCell ref="E154:E158"/>
+    <mergeCell ref="F154:F158"/>
+    <mergeCell ref="G154:G158"/>
+    <mergeCell ref="H154:H158"/>
+    <mergeCell ref="I154:I158"/>
+    <mergeCell ref="J154:J158"/>
+    <mergeCell ref="C148:C152"/>
+    <mergeCell ref="D148:D152"/>
+    <mergeCell ref="E148:E152"/>
+    <mergeCell ref="F148:F152"/>
+    <mergeCell ref="G148:G152"/>
+    <mergeCell ref="H148:H152"/>
+    <mergeCell ref="I138:I142"/>
+    <mergeCell ref="J138:J142"/>
+    <mergeCell ref="C143:C147"/>
+    <mergeCell ref="D143:D147"/>
+    <mergeCell ref="E143:E147"/>
+    <mergeCell ref="F143:F147"/>
+    <mergeCell ref="G143:G147"/>
+    <mergeCell ref="H143:H147"/>
+    <mergeCell ref="I143:I147"/>
+    <mergeCell ref="J143:J147"/>
+    <mergeCell ref="C138:C142"/>
+    <mergeCell ref="D138:D142"/>
+    <mergeCell ref="E138:E142"/>
+    <mergeCell ref="F138:F142"/>
+    <mergeCell ref="G138:G142"/>
+    <mergeCell ref="H138:H142"/>
+    <mergeCell ref="I127:I131"/>
+    <mergeCell ref="J127:J131"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="D132:D136"/>
+    <mergeCell ref="E132:E136"/>
+    <mergeCell ref="F132:F136"/>
+    <mergeCell ref="G132:G136"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="I132:I136"/>
+    <mergeCell ref="J132:J136"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="E127:E131"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="G127:G131"/>
+    <mergeCell ref="H127:H131"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="J115:J119"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="G122:G126"/>
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="I122:I126"/>
+    <mergeCell ref="J122:J126"/>
+    <mergeCell ref="C115:C119"/>
+    <mergeCell ref="D115:D119"/>
+    <mergeCell ref="E115:E119"/>
+    <mergeCell ref="F115:F119"/>
+    <mergeCell ref="G115:G119"/>
+    <mergeCell ref="H115:H119"/>
+    <mergeCell ref="I105:I109"/>
+    <mergeCell ref="J105:J109"/>
+    <mergeCell ref="C110:C114"/>
+    <mergeCell ref="D110:D114"/>
+    <mergeCell ref="E110:E114"/>
+    <mergeCell ref="F110:F114"/>
+    <mergeCell ref="G110:G114"/>
+    <mergeCell ref="H110:H114"/>
+    <mergeCell ref="I110:I114"/>
+    <mergeCell ref="J110:J114"/>
+    <mergeCell ref="C105:C109"/>
+    <mergeCell ref="D105:D109"/>
+    <mergeCell ref="E105:E109"/>
+    <mergeCell ref="F105:F109"/>
+    <mergeCell ref="G105:G109"/>
+    <mergeCell ref="H105:H109"/>
+    <mergeCell ref="I94:I98"/>
+    <mergeCell ref="J94:J98"/>
+    <mergeCell ref="C99:C103"/>
+    <mergeCell ref="D99:D103"/>
+    <mergeCell ref="E99:E103"/>
+    <mergeCell ref="F99:F103"/>
+    <mergeCell ref="G99:G103"/>
+    <mergeCell ref="H99:H103"/>
+    <mergeCell ref="I99:I103"/>
+    <mergeCell ref="J99:J103"/>
+    <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
+    <mergeCell ref="E94:E98"/>
+    <mergeCell ref="F94:F98"/>
+    <mergeCell ref="G94:G98"/>
+    <mergeCell ref="H94:H98"/>
+    <mergeCell ref="I83:I87"/>
+    <mergeCell ref="J83:J87"/>
+    <mergeCell ref="C89:C93"/>
+    <mergeCell ref="D89:D93"/>
+    <mergeCell ref="E89:E93"/>
+    <mergeCell ref="F89:F93"/>
+    <mergeCell ref="G89:G93"/>
+    <mergeCell ref="H89:H93"/>
+    <mergeCell ref="I89:I93"/>
+    <mergeCell ref="J89:J93"/>
+    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="D83:D87"/>
+    <mergeCell ref="E83:E87"/>
+    <mergeCell ref="F83:F87"/>
+    <mergeCell ref="G83:G87"/>
+    <mergeCell ref="H83:H87"/>
+    <mergeCell ref="I73:I77"/>
+    <mergeCell ref="J73:J77"/>
+    <mergeCell ref="C78:C82"/>
+    <mergeCell ref="D78:D82"/>
+    <mergeCell ref="E78:E82"/>
+    <mergeCell ref="F78:F82"/>
+    <mergeCell ref="G78:G82"/>
+    <mergeCell ref="H78:H82"/>
+    <mergeCell ref="I78:I82"/>
+    <mergeCell ref="J78:J82"/>
+    <mergeCell ref="C73:C77"/>
+    <mergeCell ref="D73:D77"/>
+    <mergeCell ref="E73:E77"/>
+    <mergeCell ref="F73:F77"/>
+    <mergeCell ref="G73:G77"/>
+    <mergeCell ref="H73:H77"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F66:F70"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="I66:I70"/>
+    <mergeCell ref="J66:J70"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="F61:F65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="D56:D60"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="I56:I60"/>
+    <mergeCell ref="J56:J60"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I40:I44"/>
+    <mergeCell ref="J40:J44"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="J45:J49"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="H40:H44"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="G24:G28"/>
+    <mergeCell ref="H24:H28"/>
+    <mergeCell ref="I24:I28"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
